--- a/research/traditional_assets/database/data/slovenia/slovenia_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_software_system_application.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1216096305012065</v>
+        <v>0.1214150222032542</v>
       </c>
       <c r="C2">
-        <v>37.5203425724814</v>
+        <v>37.19355027105266</v>
       </c>
       <c r="D2">
-        <v>34.71034257248139</v>
+        <v>34.75945027105266</v>
       </c>
       <c r="E2">
-        <v>-1.79</v>
+        <v>-1.4141</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3759</v>
       </c>
       <c r="G2">
         <v>2.81</v>
@@ -1445,28 +1445,28 @@
         <v>1.37</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01890777</v>
       </c>
       <c r="N2">
-        <v>1.37</v>
+        <v>1.35109223</v>
       </c>
       <c r="O2">
-        <v>0.2602999999999999</v>
+        <v>0.2567075236999999</v>
       </c>
       <c r="P2">
-        <v>1.1097</v>
+        <v>1.0943847063</v>
       </c>
       <c r="Q2">
-        <v>5.0497</v>
+        <v>5.034384706299999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1216096305012065</v>
+        <v>0.1222298911143982</v>
       </c>
       <c r="T2">
-        <v>1.278259280003682</v>
+        <v>1.288717765021894</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>72.45698461531951</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1214150222032542</v>
+        <v>0.1212204139053019</v>
       </c>
       <c r="C3">
-        <v>37.19355027105266</v>
+        <v>36.86689712023802</v>
       </c>
       <c r="D3">
-        <v>34.75945027105266</v>
+        <v>34.80869712023802</v>
       </c>
       <c r="E3">
-        <v>-1.4141</v>
+        <v>-1.0382</v>
       </c>
       <c r="F3">
-        <v>0.3759</v>
+        <v>0.7517999999999999</v>
       </c>
       <c r="G3">
         <v>2.81</v>
@@ -1527,28 +1527,28 @@
         <v>1.37</v>
       </c>
       <c r="M3">
-        <v>0.01890777</v>
+        <v>0.03781553999999999</v>
       </c>
       <c r="N3">
-        <v>1.35109223</v>
+        <v>1.33218446</v>
       </c>
       <c r="O3">
-        <v>0.2567075236999999</v>
+        <v>0.2531150474</v>
       </c>
       <c r="P3">
-        <v>1.0943847063</v>
+        <v>1.0790694126</v>
       </c>
       <c r="Q3">
-        <v>5.034384706299999</v>
+        <v>5.0190694126</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1222298911143982</v>
+        <v>0.1228628101074509</v>
       </c>
       <c r="T3">
-        <v>1.288717765021894</v>
+        <v>1.299389688509865</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>72.45698461531951</v>
+        <v>36.22849230765976</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1212204139053019</v>
+        <v>0.1210258056073496</v>
       </c>
       <c r="C4">
-        <v>36.86689712023802</v>
+        <v>36.5403837123183</v>
       </c>
       <c r="D4">
-        <v>34.80869712023802</v>
+        <v>34.8580837123183</v>
       </c>
       <c r="E4">
-        <v>-1.0382</v>
+        <v>-0.6623000000000001</v>
       </c>
       <c r="F4">
-        <v>0.7517999999999999</v>
+        <v>1.1277</v>
       </c>
       <c r="G4">
         <v>2.81</v>
@@ -1609,28 +1609,28 @@
         <v>1.37</v>
       </c>
       <c r="M4">
-        <v>0.03781553999999999</v>
+        <v>0.05672330999999999</v>
       </c>
       <c r="N4">
-        <v>1.33218446</v>
+        <v>1.31327669</v>
       </c>
       <c r="O4">
-        <v>0.2531150474</v>
+        <v>0.2495225711</v>
       </c>
       <c r="P4">
-        <v>1.0790694126</v>
+        <v>1.0637541189</v>
       </c>
       <c r="Q4">
-        <v>5.0190694126</v>
+        <v>5.0037541189</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1228628101074509</v>
+        <v>0.1235087789766491</v>
       </c>
       <c r="T4">
-        <v>1.299389688509865</v>
+        <v>1.310281651657383</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>36.22849230765976</v>
+        <v>24.15232820510651</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1210258056073496</v>
+        <v>0.1208311973093973</v>
       </c>
       <c r="C5">
-        <v>36.5403837123183</v>
+        <v>36.21401064294041</v>
       </c>
       <c r="D5">
-        <v>34.8580837123183</v>
+        <v>34.9076106429404</v>
       </c>
       <c r="E5">
-        <v>-0.6623000000000001</v>
+        <v>-0.2864000000000002</v>
       </c>
       <c r="F5">
-        <v>1.1277</v>
+        <v>1.5036</v>
       </c>
       <c r="G5">
         <v>2.81</v>
@@ -1691,28 +1691,28 @@
         <v>1.37</v>
       </c>
       <c r="M5">
-        <v>0.05672330999999999</v>
+        <v>0.07563107999999999</v>
       </c>
       <c r="N5">
-        <v>1.31327669</v>
+        <v>1.29436892</v>
       </c>
       <c r="O5">
-        <v>0.2495225711</v>
+        <v>0.2459300947999999</v>
       </c>
       <c r="P5">
-        <v>1.0637541189</v>
+        <v>1.0484388252</v>
       </c>
       <c r="Q5">
-        <v>5.0037541189</v>
+        <v>4.988438825199999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1235087789766491</v>
+        <v>0.1241682055306222</v>
       </c>
       <c r="T5">
-        <v>1.310281651657383</v>
+        <v>1.321400530703806</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>24.15232820510651</v>
+        <v>18.11424615382988</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1208311973093973</v>
+        <v>0.120636589011445</v>
       </c>
       <c r="C6">
-        <v>36.21401064294041</v>
+        <v>35.8877785111413</v>
       </c>
       <c r="D6">
-        <v>34.9076106429404</v>
+        <v>34.9572785111413</v>
       </c>
       <c r="E6">
-        <v>-0.2864000000000002</v>
+        <v>0.08949999999999991</v>
       </c>
       <c r="F6">
-        <v>1.5036</v>
+        <v>1.8795</v>
       </c>
       <c r="G6">
         <v>2.81</v>
@@ -1773,28 +1773,28 @@
         <v>1.37</v>
       </c>
       <c r="M6">
-        <v>0.07563107999999999</v>
+        <v>0.09453884999999999</v>
       </c>
       <c r="N6">
-        <v>1.29436892</v>
+        <v>1.27546115</v>
       </c>
       <c r="O6">
-        <v>0.2459300947999999</v>
+        <v>0.2423376184999999</v>
       </c>
       <c r="P6">
-        <v>1.0484388252</v>
+        <v>1.0331235315</v>
       </c>
       <c r="Q6">
-        <v>4.988438825199999</v>
+        <v>4.9731235315</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1241682055306222</v>
+        <v>0.1248415147488895</v>
       </c>
       <c r="T6">
-        <v>1.321400530703806</v>
+        <v>1.332753491414365</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>18.11424615382988</v>
+        <v>14.4913969230639</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.120636589011445</v>
+        <v>0.1205148807134927</v>
       </c>
       <c r="C7">
-        <v>35.8877785111413</v>
+        <v>35.54301276576135</v>
       </c>
       <c r="D7">
-        <v>34.9572785111413</v>
+        <v>34.98841276576135</v>
       </c>
       <c r="E7">
-        <v>0.08949999999999991</v>
+        <v>0.4653999999999998</v>
       </c>
       <c r="F7">
-        <v>1.8795</v>
+        <v>2.2554</v>
       </c>
       <c r="G7">
         <v>2.81</v>
@@ -1855,45 +1855,45 @@
         <v>1.37</v>
       </c>
       <c r="M7">
-        <v>0.09453884999999999</v>
+        <v>0.11682972</v>
       </c>
       <c r="N7">
-        <v>1.27546115</v>
+        <v>1.25317028</v>
       </c>
       <c r="O7">
-        <v>0.2423376184999999</v>
+        <v>0.2381023531999999</v>
       </c>
       <c r="P7">
-        <v>1.0331235315</v>
+        <v>1.0150679268</v>
       </c>
       <c r="Q7">
-        <v>4.9731235315</v>
+        <v>4.9550679268</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1248415147488895</v>
+        <v>0.125529149695205</v>
       </c>
       <c r="T7">
-        <v>1.332753491414365</v>
+        <v>1.344348004480468</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.19</v>
       </c>
       <c r="W7">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>14.4913969230639</v>
+        <v>11.7264682308577</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1205148807134927</v>
+        <v>0.1203324224155405</v>
       </c>
       <c r="C8">
-        <v>35.54301276576135</v>
+        <v>35.21389153427582</v>
       </c>
       <c r="D8">
-        <v>34.98841276576135</v>
+        <v>35.03519153427582</v>
       </c>
       <c r="E8">
-        <v>0.4653999999999998</v>
+        <v>0.8412999999999995</v>
       </c>
       <c r="F8">
-        <v>2.2554</v>
+        <v>2.6313</v>
       </c>
       <c r="G8">
         <v>2.81</v>
@@ -1937,28 +1937,28 @@
         <v>1.37</v>
       </c>
       <c r="M8">
-        <v>0.11682972</v>
+        <v>0.13630134</v>
       </c>
       <c r="N8">
-        <v>1.25317028</v>
+        <v>1.23369866</v>
       </c>
       <c r="O8">
-        <v>0.2381023531999999</v>
+        <v>0.2344027453999999</v>
       </c>
       <c r="P8">
-        <v>1.0150679268</v>
+        <v>0.9992959145999998</v>
       </c>
       <c r="Q8">
-        <v>4.9550679268</v>
+        <v>4.9392959146</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.125529149695205</v>
+        <v>0.1262315724898284</v>
       </c>
       <c r="T8">
-        <v>1.344348004480468</v>
+        <v>1.356191861913584</v>
       </c>
       <c r="U8">
         <v>0.0518</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.7264682308577</v>
+        <v>10.05125848359231</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1203324224155404</v>
+        <v>0.1202601241175882</v>
       </c>
       <c r="C9">
-        <v>35.21389153427582</v>
+        <v>34.85656203573887</v>
       </c>
       <c r="D9">
-        <v>35.03519153427582</v>
+        <v>35.05376203573886</v>
       </c>
       <c r="E9">
-        <v>0.8412999999999999</v>
+        <v>1.2172</v>
       </c>
       <c r="F9">
-        <v>2.6313</v>
+        <v>3.0072</v>
       </c>
       <c r="G9">
         <v>2.81</v>
@@ -2019,45 +2019,45 @@
         <v>1.37</v>
       </c>
       <c r="M9">
-        <v>0.13630134</v>
+        <v>0.1608852</v>
       </c>
       <c r="N9">
-        <v>1.23369866</v>
+        <v>1.2091148</v>
       </c>
       <c r="O9">
-        <v>0.2344027453999999</v>
+        <v>0.2297318119999999</v>
       </c>
       <c r="P9">
-        <v>0.9992959145999998</v>
+        <v>0.9793829879999997</v>
       </c>
       <c r="Q9">
-        <v>4.9392959146</v>
+        <v>4.919382988</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1262315724898284</v>
+        <v>0.1269492653452045</v>
       </c>
       <c r="T9">
-        <v>1.356191861913584</v>
+        <v>1.368293194508289</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.19</v>
       </c>
       <c r="W9">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.05125848359231</v>
+        <v>8.515388612501335</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1202601241175882</v>
+        <v>0.1201497558196359</v>
       </c>
       <c r="C10">
-        <v>34.85656203573887</v>
+        <v>34.50904917301256</v>
       </c>
       <c r="D10">
-        <v>35.05376203573886</v>
+        <v>35.08214917301255</v>
       </c>
       <c r="E10">
-        <v>1.2172</v>
+        <v>1.593099999999999</v>
       </c>
       <c r="F10">
-        <v>3.0072</v>
+        <v>3.383099999999999</v>
       </c>
       <c r="G10">
         <v>2.81</v>
@@ -2101,45 +2101,45 @@
         <v>1.37</v>
       </c>
       <c r="M10">
-        <v>0.1608852</v>
+        <v>0.18370233</v>
       </c>
       <c r="N10">
-        <v>1.2091148</v>
+        <v>1.18629767</v>
       </c>
       <c r="O10">
-        <v>0.2297318119999999</v>
+        <v>0.2253965572999999</v>
       </c>
       <c r="P10">
-        <v>0.9793829879999997</v>
+        <v>0.9609011126999997</v>
       </c>
       <c r="Q10">
-        <v>4.919382988</v>
+        <v>4.9009011127</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1269492653452045</v>
+        <v>0.1276827316699295</v>
       </c>
       <c r="T10">
-        <v>1.368293194508289</v>
+        <v>1.380660490456724</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0.19</v>
       </c>
       <c r="W10">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>8.515388612501335</v>
+        <v>7.457717057807595</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1201497558196359</v>
+        <v>0.1199875475216836</v>
       </c>
       <c r="C11">
-        <v>34.50904917301256</v>
+        <v>34.17495329216588</v>
       </c>
       <c r="D11">
-        <v>35.08214917301255</v>
+        <v>35.12395329216588</v>
       </c>
       <c r="E11">
-        <v>1.593099999999999</v>
+        <v>1.968999999999999</v>
       </c>
       <c r="F11">
-        <v>3.383099999999999</v>
+        <v>3.758999999999999</v>
       </c>
       <c r="G11">
         <v>2.81</v>
@@ -2183,28 +2183,28 @@
         <v>1.37</v>
       </c>
       <c r="M11">
-        <v>0.18370233</v>
+        <v>0.2041137</v>
       </c>
       <c r="N11">
-        <v>1.18629767</v>
+        <v>1.1658863</v>
       </c>
       <c r="O11">
-        <v>0.2253965572999999</v>
+        <v>0.221518397</v>
       </c>
       <c r="P11">
-        <v>0.9609011126999997</v>
+        <v>0.9443679029999997</v>
       </c>
       <c r="Q11">
-        <v>4.9009011127</v>
+        <v>4.884367902999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1276827316699295</v>
+        <v>0.1284324972463151</v>
       </c>
       <c r="T11">
-        <v>1.380660490456724</v>
+        <v>1.393302615204013</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.457717057807595</v>
+        <v>6.711945352026835</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1199875475216836</v>
+        <v>0.1199144392237313</v>
       </c>
       <c r="C12">
-        <v>34.17495329216588</v>
+        <v>33.81792725909214</v>
       </c>
       <c r="D12">
-        <v>35.12395329216588</v>
+        <v>35.14282725909214</v>
       </c>
       <c r="E12">
-        <v>1.969</v>
+        <v>2.3449</v>
       </c>
       <c r="F12">
-        <v>3.759</v>
+        <v>4.1349</v>
       </c>
       <c r="G12">
         <v>2.81</v>
@@ -2265,45 +2265,45 @@
         <v>1.37</v>
       </c>
       <c r="M12">
-        <v>0.2041137</v>
+        <v>0.22865997</v>
       </c>
       <c r="N12">
-        <v>1.1658863</v>
+        <v>1.14134003</v>
       </c>
       <c r="O12">
-        <v>0.221518397</v>
+        <v>0.2168546056999999</v>
       </c>
       <c r="P12">
-        <v>0.9443679029999997</v>
+        <v>0.9244854242999997</v>
       </c>
       <c r="Q12">
-        <v>4.884367902999999</v>
+        <v>4.8644854243</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1284324972463151</v>
+        <v>0.1291991114873385</v>
       </c>
       <c r="T12">
-        <v>1.393302615204013</v>
+        <v>1.406228832642253</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0.19</v>
       </c>
       <c r="W12">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.711945352026834</v>
+        <v>5.991429107595875</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1199144392237313</v>
+        <v>0.119760330925779</v>
       </c>
       <c r="C13">
-        <v>33.81792725909214</v>
+        <v>33.48187906956871</v>
       </c>
       <c r="D13">
-        <v>35.14282725909214</v>
+        <v>35.18267906956871</v>
       </c>
       <c r="E13">
-        <v>2.3449</v>
+        <v>2.7208</v>
       </c>
       <c r="F13">
-        <v>4.1349</v>
+        <v>4.5108</v>
       </c>
       <c r="G13">
         <v>2.81</v>
@@ -2347,28 +2347,28 @@
         <v>1.37</v>
       </c>
       <c r="M13">
-        <v>0.22865997</v>
+        <v>0.24944724</v>
       </c>
       <c r="N13">
-        <v>1.14134003</v>
+        <v>1.12055276</v>
       </c>
       <c r="O13">
-        <v>0.2168546056999999</v>
+        <v>0.2129050243999999</v>
       </c>
       <c r="P13">
-        <v>0.9244854242999997</v>
+        <v>0.9076477355999997</v>
       </c>
       <c r="Q13">
-        <v>4.8644854243</v>
+        <v>4.8476477356</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1291991114873385</v>
+        <v>0.1299831487792943</v>
       </c>
       <c r="T13">
-        <v>1.406228832642253</v>
+        <v>1.419448827749543</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.991429107595875</v>
+        <v>5.492143348629552</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.119760330925779</v>
+        <v>0.1196062226278267</v>
       </c>
       <c r="C14">
-        <v>33.48187906956871</v>
+        <v>33.14592136620938</v>
       </c>
       <c r="D14">
-        <v>35.18267906956871</v>
+        <v>35.22262136620937</v>
       </c>
       <c r="E14">
-        <v>2.7208</v>
+        <v>3.096699999999999</v>
       </c>
       <c r="F14">
-        <v>4.5108</v>
+        <v>4.886699999999999</v>
       </c>
       <c r="G14">
         <v>2.81</v>
@@ -2429,28 +2429,28 @@
         <v>1.37</v>
       </c>
       <c r="M14">
-        <v>0.24944724</v>
+        <v>0.27023451</v>
       </c>
       <c r="N14">
-        <v>1.12055276</v>
+        <v>1.09976549</v>
       </c>
       <c r="O14">
-        <v>0.2129050243999999</v>
+        <v>0.2089554431</v>
       </c>
       <c r="P14">
-        <v>0.9076477355999997</v>
+        <v>0.8908100468999998</v>
       </c>
       <c r="Q14">
-        <v>4.8476477356</v>
+        <v>4.8308100469</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1299831487792943</v>
+        <v>0.1307852099170422</v>
       </c>
       <c r="T14">
-        <v>1.419448827749543</v>
+        <v>1.432972730790334</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.492143348629552</v>
+        <v>5.069670783350356</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1196062226278267</v>
+        <v>0.1194521143298744</v>
       </c>
       <c r="C15">
-        <v>33.14592136620938</v>
+        <v>32.81005445754661</v>
       </c>
       <c r="D15">
-        <v>35.22262136620937</v>
+        <v>35.2626544575466</v>
       </c>
       <c r="E15">
-        <v>3.096699999999999</v>
+        <v>3.4726</v>
       </c>
       <c r="F15">
-        <v>4.886699999999999</v>
+        <v>5.2626</v>
       </c>
       <c r="G15">
         <v>2.81</v>
@@ -2511,28 +2511,28 @@
         <v>1.37</v>
       </c>
       <c r="M15">
-        <v>0.27023451</v>
+        <v>0.29102178</v>
       </c>
       <c r="N15">
-        <v>1.09976549</v>
+        <v>1.07897822</v>
       </c>
       <c r="O15">
-        <v>0.2089554431</v>
+        <v>0.2050058618</v>
       </c>
       <c r="P15">
-        <v>0.8908100468999998</v>
+        <v>0.8739723581999999</v>
       </c>
       <c r="Q15">
-        <v>4.8308100469</v>
+        <v>4.8139723582</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1307852099170422</v>
+        <v>0.1316059236393889</v>
       </c>
       <c r="T15">
-        <v>1.432972730790334</v>
+        <v>1.446811143204167</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.069670783350356</v>
+        <v>4.707551441682474</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1194521143298744</v>
+        <v>0.1196017560319221</v>
       </c>
       <c r="C16">
-        <v>32.81005445754661</v>
+        <v>32.39528038567548</v>
       </c>
       <c r="D16">
-        <v>35.2626544575466</v>
+        <v>35.22378038567548</v>
       </c>
       <c r="E16">
-        <v>3.4726</v>
+        <v>3.8485</v>
       </c>
       <c r="F16">
-        <v>5.2626</v>
+        <v>5.638500000000001</v>
       </c>
       <c r="G16">
         <v>2.81</v>
@@ -2593,45 +2593,45 @@
         <v>1.37</v>
       </c>
       <c r="M16">
-        <v>0.29102178</v>
+        <v>0.3259053000000001</v>
       </c>
       <c r="N16">
-        <v>1.07897822</v>
+        <v>1.0440947</v>
       </c>
       <c r="O16">
-        <v>0.2050058618</v>
+        <v>0.1983779929999999</v>
       </c>
       <c r="P16">
-        <v>0.8739723581999999</v>
+        <v>0.8457167069999997</v>
       </c>
       <c r="Q16">
-        <v>4.8139723582</v>
+        <v>4.785716707</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1316059236393889</v>
+        <v>0.1324459482728496</v>
       </c>
       <c r="T16">
-        <v>1.446811143204167</v>
+        <v>1.460975165321855</v>
       </c>
       <c r="U16">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V16">
         <v>0.19</v>
       </c>
       <c r="W16">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.707551441682474</v>
+        <v>4.203675116667324</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1196017560319221</v>
+        <v>0.1199214977339698</v>
       </c>
       <c r="C17">
-        <v>32.39528038567548</v>
+        <v>31.93660411774134</v>
       </c>
       <c r="D17">
-        <v>35.22378038567548</v>
+        <v>35.14100411774133</v>
       </c>
       <c r="E17">
-        <v>3.8485</v>
+        <v>4.224399999999999</v>
       </c>
       <c r="F17">
-        <v>5.6385</v>
+        <v>6.014399999999999</v>
       </c>
       <c r="G17">
         <v>2.81</v>
@@ -2675,45 +2675,45 @@
         <v>1.37</v>
       </c>
       <c r="M17">
-        <v>0.3259053</v>
+        <v>0.36868272</v>
       </c>
       <c r="N17">
-        <v>1.0440947</v>
+        <v>1.00131728</v>
       </c>
       <c r="O17">
-        <v>0.1983779929999999</v>
+        <v>0.1902502831999999</v>
       </c>
       <c r="P17">
-        <v>0.8457167069999997</v>
+        <v>0.8110669967999997</v>
       </c>
       <c r="Q17">
-        <v>4.785716707</v>
+        <v>4.7510669968</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1324459482728496</v>
+        <v>0.1333059734928212</v>
       </c>
       <c r="T17">
-        <v>1.460975165321855</v>
+        <v>1.475476426061393</v>
       </c>
       <c r="U17">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V17">
         <v>0.19</v>
       </c>
       <c r="W17">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.203675116667325</v>
+        <v>3.715932224868038</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1199214977339698</v>
+        <v>0.1202015494360175</v>
       </c>
       <c r="C18">
-        <v>31.93660411774134</v>
+        <v>31.48852193875847</v>
       </c>
       <c r="D18">
-        <v>35.14100411774133</v>
+        <v>35.06882193875847</v>
       </c>
       <c r="E18">
-        <v>4.224399999999999</v>
+        <v>4.6003</v>
       </c>
       <c r="F18">
-        <v>6.014399999999999</v>
+        <v>6.3903</v>
       </c>
       <c r="G18">
         <v>2.81</v>
@@ -2757,45 +2757,45 @@
         <v>1.37</v>
       </c>
       <c r="M18">
-        <v>0.36868272</v>
+        <v>0.40961823</v>
       </c>
       <c r="N18">
-        <v>1.00131728</v>
+        <v>0.9603817699999997</v>
       </c>
       <c r="O18">
-        <v>0.1902502831999999</v>
+        <v>0.1824725362999999</v>
       </c>
       <c r="P18">
-        <v>0.8110669967999997</v>
+        <v>0.7779092336999998</v>
       </c>
       <c r="Q18">
-        <v>4.7510669968</v>
+        <v>4.717909233699999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1333059734928212</v>
+        <v>0.1341867222120693</v>
       </c>
       <c r="T18">
-        <v>1.475476426061393</v>
+        <v>1.490327114770558</v>
       </c>
       <c r="U18">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V18">
         <v>0.19</v>
       </c>
       <c r="W18">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>3.715932224868038</v>
+        <v>3.344577705928761</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1202015494360175</v>
+        <v>0.1201187211380652</v>
       </c>
       <c r="C19">
-        <v>31.48852193875847</v>
+        <v>31.13393969239893</v>
       </c>
       <c r="D19">
-        <v>35.06882193875847</v>
+        <v>35.09013969239893</v>
       </c>
       <c r="E19">
-        <v>4.6003</v>
+        <v>4.9762</v>
       </c>
       <c r="F19">
-        <v>6.3903</v>
+        <v>6.7662</v>
       </c>
       <c r="G19">
         <v>2.81</v>
@@ -2839,28 +2839,28 @@
         <v>1.37</v>
       </c>
       <c r="M19">
-        <v>0.40961823</v>
+        <v>0.4337134200000001</v>
       </c>
       <c r="N19">
-        <v>0.9603817699999997</v>
+        <v>0.9362865799999995</v>
       </c>
       <c r="O19">
-        <v>0.1824725362999999</v>
+        <v>0.1778944501999999</v>
       </c>
       <c r="P19">
-        <v>0.7779092336999998</v>
+        <v>0.7583921297999996</v>
       </c>
       <c r="Q19">
-        <v>4.717909233699999</v>
+        <v>4.698392129799999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1341867222120693</v>
+        <v>0.1350889526073966</v>
       </c>
       <c r="T19">
-        <v>1.490327114770558</v>
+        <v>1.505540015399458</v>
       </c>
       <c r="U19">
         <v>0.0641</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.344577705928761</v>
+        <v>3.158767833377162</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1201187211380652</v>
+        <v>0.1212363128401129</v>
       </c>
       <c r="C20">
-        <v>31.13393969239893</v>
+        <v>30.47256856125224</v>
       </c>
       <c r="D20">
-        <v>35.09013969239892</v>
+        <v>34.80466856125224</v>
       </c>
       <c r="E20">
-        <v>4.976199999999999</v>
+        <v>5.352099999999999</v>
       </c>
       <c r="F20">
-        <v>6.766199999999999</v>
+        <v>7.142099999999999</v>
       </c>
       <c r="G20">
         <v>2.81</v>
@@ -2921,45 +2921,45 @@
         <v>1.37</v>
       </c>
       <c r="M20">
-        <v>0.43371342</v>
+        <v>0.51351699</v>
       </c>
       <c r="N20">
-        <v>0.9362865799999998</v>
+        <v>0.8564830099999997</v>
       </c>
       <c r="O20">
-        <v>0.1778944501999999</v>
+        <v>0.1627317719</v>
       </c>
       <c r="P20">
-        <v>0.7583921297999998</v>
+        <v>0.6937512380999997</v>
       </c>
       <c r="Q20">
-        <v>4.6983921298</v>
+        <v>4.633751238099999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1350889526073966</v>
+        <v>0.1360134602964357</v>
       </c>
       <c r="T20">
-        <v>1.505540015399458</v>
+        <v>1.521128543204381</v>
       </c>
       <c r="U20">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V20">
         <v>0.19</v>
       </c>
       <c r="W20">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.158767833377164</v>
+        <v>2.667876675317013</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1212363128401129</v>
+        <v>0.1212166645421607</v>
       </c>
       <c r="C21">
-        <v>30.47256856125224</v>
+        <v>30.10164729026023</v>
       </c>
       <c r="D21">
-        <v>34.80466856125224</v>
+        <v>34.80964729026023</v>
       </c>
       <c r="E21">
-        <v>5.352099999999999</v>
+        <v>5.728</v>
       </c>
       <c r="F21">
-        <v>7.142099999999999</v>
+        <v>7.518</v>
       </c>
       <c r="G21">
         <v>2.81</v>
@@ -3003,28 +3003,28 @@
         <v>1.37</v>
       </c>
       <c r="M21">
-        <v>0.51351699</v>
+        <v>0.5405442</v>
       </c>
       <c r="N21">
-        <v>0.8564830099999997</v>
+        <v>0.8294557999999996</v>
       </c>
       <c r="O21">
-        <v>0.1627317719</v>
+        <v>0.1575966019999999</v>
       </c>
       <c r="P21">
-        <v>0.6937512380999997</v>
+        <v>0.6718591979999997</v>
       </c>
       <c r="Q21">
-        <v>4.633751238099999</v>
+        <v>4.611859197999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1360134602964357</v>
+        <v>0.1369610806777008</v>
       </c>
       <c r="T21">
-        <v>1.521128543204381</v>
+        <v>1.537106784204427</v>
       </c>
       <c r="U21">
         <v>0.07190000000000001</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.667876675317013</v>
+        <v>2.534482841551162</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1212166645421607</v>
+        <v>0.1218604062442084</v>
       </c>
       <c r="C22">
-        <v>30.10164729026023</v>
+        <v>29.56336574807264</v>
       </c>
       <c r="D22">
-        <v>34.80964729026023</v>
+        <v>34.64726574807264</v>
       </c>
       <c r="E22">
-        <v>5.728</v>
+        <v>6.1039</v>
       </c>
       <c r="F22">
-        <v>7.518</v>
+        <v>7.8939</v>
       </c>
       <c r="G22">
         <v>2.81</v>
@@ -3085,45 +3085,45 @@
         <v>1.37</v>
       </c>
       <c r="M22">
-        <v>0.5405442</v>
+        <v>0.59835762</v>
       </c>
       <c r="N22">
-        <v>0.8294557999999996</v>
+        <v>0.7716423799999996</v>
       </c>
       <c r="O22">
-        <v>0.1575966019999999</v>
+        <v>0.1466120521999999</v>
       </c>
       <c r="P22">
-        <v>0.6718591979999997</v>
+        <v>0.6250303277999997</v>
       </c>
       <c r="Q22">
-        <v>4.611859197999999</v>
+        <v>4.5650303278</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1369610806777008</v>
+        <v>0.137932691448365</v>
       </c>
       <c r="T22">
-        <v>1.537106784204427</v>
+        <v>1.553489537634855</v>
       </c>
       <c r="U22">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V22">
         <v>0.19</v>
       </c>
       <c r="W22">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.534482841551162</v>
+        <v>2.28960065721232</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1218604062442084</v>
+        <v>0.1218723479462561</v>
       </c>
       <c r="C23">
-        <v>29.56336574807264</v>
+        <v>29.18446780754498</v>
       </c>
       <c r="D23">
-        <v>34.64726574807264</v>
+        <v>34.64426780754498</v>
       </c>
       <c r="E23">
-        <v>6.103899999999999</v>
+        <v>6.4798</v>
       </c>
       <c r="F23">
-        <v>7.893899999999999</v>
+        <v>8.2698</v>
       </c>
       <c r="G23">
         <v>2.81</v>
@@ -3167,28 +3167,28 @@
         <v>1.37</v>
       </c>
       <c r="M23">
-        <v>0.5983576199999999</v>
+        <v>0.62685084</v>
       </c>
       <c r="N23">
-        <v>0.7716423799999997</v>
+        <v>0.7431491599999996</v>
       </c>
       <c r="O23">
-        <v>0.1466120522</v>
+        <v>0.1411983403999999</v>
       </c>
       <c r="P23">
-        <v>0.6250303277999998</v>
+        <v>0.6019508195999997</v>
       </c>
       <c r="Q23">
-        <v>4.5650303278</v>
+        <v>4.541950819599999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.137932691448365</v>
+        <v>0.1389292153157129</v>
       </c>
       <c r="T23">
-        <v>1.553489537634855</v>
+        <v>1.570292361666062</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.28960065721232</v>
+        <v>2.185527900066305</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1218723479462561</v>
+        <v>0.1218842896483038</v>
       </c>
       <c r="C24">
-        <v>29.18446780754498</v>
+        <v>28.8055703857809</v>
       </c>
       <c r="D24">
-        <v>34.64426780754498</v>
+        <v>34.6412703857809</v>
       </c>
       <c r="E24">
-        <v>6.4798</v>
+        <v>6.8557</v>
       </c>
       <c r="F24">
-        <v>8.2698</v>
+        <v>8.6457</v>
       </c>
       <c r="G24">
         <v>2.81</v>
@@ -3249,28 +3249,28 @@
         <v>1.37</v>
       </c>
       <c r="M24">
-        <v>0.62685084</v>
+        <v>0.65534406</v>
       </c>
       <c r="N24">
-        <v>0.7431491599999996</v>
+        <v>0.7146559399999997</v>
       </c>
       <c r="O24">
-        <v>0.1411983403999999</v>
+        <v>0.1357846285999999</v>
       </c>
       <c r="P24">
-        <v>0.6019508195999997</v>
+        <v>0.5788713113999997</v>
       </c>
       <c r="Q24">
-        <v>4.541950819599999</v>
+        <v>4.5188713114</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1389292153157129</v>
+        <v>0.139951622919875</v>
       </c>
       <c r="T24">
-        <v>1.570292361666062</v>
+        <v>1.587531622685092</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.185527900066305</v>
+        <v>2.09050494788951</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1218842896483038</v>
+        <v>0.1218962313503515</v>
       </c>
       <c r="C25">
-        <v>28.8055703857809</v>
+        <v>28.42667348264576</v>
       </c>
       <c r="D25">
-        <v>34.6412703857809</v>
+        <v>34.63827348264576</v>
       </c>
       <c r="E25">
-        <v>6.8557</v>
+        <v>7.231599999999999</v>
       </c>
       <c r="F25">
-        <v>8.6457</v>
+        <v>9.021599999999999</v>
       </c>
       <c r="G25">
         <v>2.81</v>
@@ -3331,28 +3331,28 @@
         <v>1.37</v>
       </c>
       <c r="M25">
-        <v>0.65534406</v>
+        <v>0.68383728</v>
       </c>
       <c r="N25">
-        <v>0.7146559399999997</v>
+        <v>0.6861627199999997</v>
       </c>
       <c r="O25">
-        <v>0.1357846285999999</v>
+        <v>0.1303709167999999</v>
       </c>
       <c r="P25">
-        <v>0.5788713113999997</v>
+        <v>0.5557918031999998</v>
       </c>
       <c r="Q25">
-        <v>4.5188713114</v>
+        <v>4.495791803199999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.139951622919875</v>
+        <v>0.1410009359873046</v>
       </c>
       <c r="T25">
-        <v>1.587531622685092</v>
+        <v>1.605224548467782</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.09050494788951</v>
+        <v>2.00340057506078</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1218962313503515</v>
+        <v>0.1247836730523992</v>
       </c>
       <c r="C26">
-        <v>28.42667348264576</v>
+        <v>27.34104677647073</v>
       </c>
       <c r="D26">
-        <v>34.63827348264576</v>
+        <v>33.92854677647072</v>
       </c>
       <c r="E26">
-        <v>7.231599999999999</v>
+        <v>7.607499999999999</v>
       </c>
       <c r="F26">
-        <v>9.021599999999999</v>
+        <v>9.397499999999999</v>
       </c>
       <c r="G26">
         <v>2.81</v>
@@ -3413,45 +3413,45 @@
         <v>1.37</v>
       </c>
       <c r="M26">
-        <v>0.68383728</v>
+        <v>0.8457749999999998</v>
       </c>
       <c r="N26">
-        <v>0.6861627199999997</v>
+        <v>0.5242249999999998</v>
       </c>
       <c r="O26">
-        <v>0.1303709167999999</v>
+        <v>0.09960274999999996</v>
       </c>
       <c r="P26">
-        <v>0.5557918031999998</v>
+        <v>0.4246222499999999</v>
       </c>
       <c r="Q26">
-        <v>4.495791803199999</v>
+        <v>4.36462225</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1410009359873046</v>
+        <v>0.1420782307365323</v>
       </c>
       <c r="T26">
-        <v>1.605224548467782</v>
+        <v>1.623389285604676</v>
       </c>
       <c r="U26">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V26">
         <v>0.19</v>
       </c>
       <c r="W26">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.00340057506078</v>
+        <v>1.61981614495581</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1247836730523992</v>
+        <v>0.1249106347544469</v>
       </c>
       <c r="C27">
-        <v>27.34104677647073</v>
+        <v>26.93460680797543</v>
       </c>
       <c r="D27">
-        <v>33.92854677647072</v>
+        <v>33.89800680797543</v>
       </c>
       <c r="E27">
-        <v>7.607499999999999</v>
+        <v>7.983399999999999</v>
       </c>
       <c r="F27">
-        <v>9.397499999999999</v>
+        <v>9.773399999999999</v>
       </c>
       <c r="G27">
         <v>2.81</v>
@@ -3495,28 +3495,28 @@
         <v>1.37</v>
       </c>
       <c r="M27">
-        <v>0.8457749999999998</v>
+        <v>0.8796059999999999</v>
       </c>
       <c r="N27">
-        <v>0.5242249999999998</v>
+        <v>0.4903939999999998</v>
       </c>
       <c r="O27">
-        <v>0.09960274999999996</v>
+        <v>0.09317485999999996</v>
       </c>
       <c r="P27">
-        <v>0.4246222499999999</v>
+        <v>0.3972191399999998</v>
       </c>
       <c r="Q27">
-        <v>4.36462225</v>
+        <v>4.33721914</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1420782307365323</v>
+        <v>0.1431846415600634</v>
       </c>
       <c r="T27">
-        <v>1.623389285604676</v>
+        <v>1.642044961583108</v>
       </c>
       <c r="U27">
         <v>0.09</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>1.61981614495581</v>
+        <v>1.557515523995971</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1249106347544469</v>
+        <v>0.1383788946071408</v>
       </c>
       <c r="C28">
-        <v>26.93460680797543</v>
+        <v>23.60403532238609</v>
       </c>
       <c r="D28">
-        <v>33.89800680797543</v>
+        <v>30.94333532238609</v>
       </c>
       <c r="E28">
-        <v>7.983399999999999</v>
+        <v>8.359300000000001</v>
       </c>
       <c r="F28">
-        <v>9.773399999999999</v>
+        <v>10.1493</v>
       </c>
       <c r="G28">
         <v>2.81</v>
@@ -3577,45 +3577,45 @@
         <v>1.37</v>
       </c>
       <c r="M28">
-        <v>0.8796059999999999</v>
+        <v>1.48991724</v>
       </c>
       <c r="N28">
-        <v>0.4903939999999998</v>
+        <v>-0.1199172400000006</v>
       </c>
       <c r="O28">
-        <v>0.09317485999999996</v>
+        <v>-0.02278427560000011</v>
       </c>
       <c r="P28">
-        <v>0.3972191399999998</v>
+        <v>-0.09713296440000048</v>
       </c>
       <c r="Q28">
-        <v>4.33721914</v>
+        <v>3.842867035599999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1431846415600634</v>
+        <v>0.1447501488038725</v>
       </c>
       <c r="T28">
-        <v>1.642044961583108</v>
+        <v>1.668441662755265</v>
       </c>
       <c r="U28">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V28">
-        <v>0.19</v>
+        <v>0.174707690475479</v>
       </c>
       <c r="W28">
-        <v>0.07290000000000001</v>
+        <v>0.1211529110381997</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y28">
-        <v>1.557515523995971</v>
+        <v>0.9195141603972576</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1383788946071408</v>
+        <v>0.1393888946071408</v>
       </c>
       <c r="C29">
-        <v>23.60403532238609</v>
+        <v>23.02718786157598</v>
       </c>
       <c r="D29">
-        <v>30.94333532238609</v>
+        <v>30.74238786157598</v>
       </c>
       <c r="E29">
-        <v>8.359300000000001</v>
+        <v>8.735199999999999</v>
       </c>
       <c r="F29">
-        <v>10.1493</v>
+        <v>10.5252</v>
       </c>
       <c r="G29">
         <v>2.81</v>
@@ -3659,37 +3659,37 @@
         <v>1.37</v>
       </c>
       <c r="M29">
-        <v>1.48991724</v>
+        <v>1.54509936</v>
       </c>
       <c r="N29">
-        <v>-0.1199172400000006</v>
+        <v>-0.1750993600000004</v>
       </c>
       <c r="O29">
-        <v>-0.02278427560000011</v>
+        <v>-0.03326887840000007</v>
       </c>
       <c r="P29">
-        <v>-0.09713296440000048</v>
+        <v>-0.1418304816000003</v>
       </c>
       <c r="Q29">
-        <v>3.842867035599999</v>
+        <v>3.7981695184</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1447501488038725</v>
+        <v>0.1461244564261485</v>
       </c>
       <c r="T29">
-        <v>1.668441662755265</v>
+        <v>1.691614463626866</v>
       </c>
       <c r="U29">
         <v>0.1468</v>
       </c>
       <c r="V29">
-        <v>0.174707690475479</v>
+        <v>0.1684681301013547</v>
       </c>
       <c r="W29">
-        <v>0.1211529110381997</v>
+        <v>0.1220688785011211</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.9195141603972576</v>
+        <v>0.8866743689544986</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1393888946071408</v>
+        <v>0.1403988946071408</v>
       </c>
       <c r="C30">
-        <v>23.02718786157598</v>
+        <v>22.45293348549268</v>
       </c>
       <c r="D30">
-        <v>30.74238786157598</v>
+        <v>30.54403348549268</v>
       </c>
       <c r="E30">
-        <v>8.735199999999999</v>
+        <v>9.1111</v>
       </c>
       <c r="F30">
-        <v>10.5252</v>
+        <v>10.9011</v>
       </c>
       <c r="G30">
         <v>2.81</v>
@@ -3741,37 +3741,37 @@
         <v>1.37</v>
       </c>
       <c r="M30">
-        <v>1.54509936</v>
+        <v>1.60028148</v>
       </c>
       <c r="N30">
-        <v>-0.1750993600000004</v>
+        <v>-0.2302814800000004</v>
       </c>
       <c r="O30">
-        <v>-0.03326887840000007</v>
+        <v>-0.04375348120000007</v>
       </c>
       <c r="P30">
-        <v>-0.1418304816000003</v>
+        <v>-0.1865279988000003</v>
       </c>
       <c r="Q30">
-        <v>3.7981695184</v>
+        <v>3.7534720012</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1461244564261485</v>
+        <v>0.1475374769391928</v>
       </c>
       <c r="T30">
-        <v>1.691614463626866</v>
+        <v>1.715440019452596</v>
       </c>
       <c r="U30">
         <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.1684681301013547</v>
+        <v>0.1626588842357908</v>
       </c>
       <c r="W30">
-        <v>0.1220688785011211</v>
+        <v>0.1229216757941859</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.8866743689544986</v>
+        <v>0.8560993907146883</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1403988946071408</v>
+        <v>0.1414088946071408</v>
       </c>
       <c r="C31">
-        <v>22.45293348549268</v>
+        <v>21.88122232302779</v>
       </c>
       <c r="D31">
-        <v>30.54403348549268</v>
+        <v>30.34822232302779</v>
       </c>
       <c r="E31">
-        <v>9.111099999999997</v>
+        <v>9.486999999999998</v>
       </c>
       <c r="F31">
-        <v>10.9011</v>
+        <v>11.277</v>
       </c>
       <c r="G31">
         <v>2.81</v>
@@ -3823,37 +3823,37 @@
         <v>1.37</v>
       </c>
       <c r="M31">
-        <v>1.60028148</v>
+        <v>1.6554636</v>
       </c>
       <c r="N31">
-        <v>-0.2302814800000001</v>
+        <v>-0.2854636000000004</v>
       </c>
       <c r="O31">
-        <v>-0.04375348120000003</v>
+        <v>-0.05423808400000007</v>
       </c>
       <c r="P31">
-        <v>-0.1865279988000001</v>
+        <v>-0.2312255160000003</v>
       </c>
       <c r="Q31">
-        <v>3.7534720012</v>
+        <v>3.708774484</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1475374769391928</v>
+        <v>0.1489908694668956</v>
       </c>
       <c r="T31">
-        <v>1.715440019452596</v>
+        <v>1.739946305444776</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.1626588842357908</v>
+        <v>0.1572369214279311</v>
       </c>
       <c r="W31">
-        <v>0.1229216757941859</v>
+        <v>0.1237176199343797</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.8560993907146884</v>
+        <v>0.827562744357532</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1414088946071408</v>
+        <v>0.1424188946071408</v>
       </c>
       <c r="C32">
-        <v>21.88122232302779</v>
+        <v>21.3120057737781</v>
       </c>
       <c r="D32">
-        <v>30.34822232302779</v>
+        <v>30.1549057737781</v>
       </c>
       <c r="E32">
-        <v>9.486999999999998</v>
+        <v>9.8629</v>
       </c>
       <c r="F32">
-        <v>11.277</v>
+        <v>11.6529</v>
       </c>
       <c r="G32">
         <v>2.81</v>
@@ -3905,37 +3905,37 @@
         <v>1.37</v>
       </c>
       <c r="M32">
-        <v>1.6554636</v>
+        <v>1.71064572</v>
       </c>
       <c r="N32">
-        <v>-0.2854636000000004</v>
+        <v>-0.3406457200000004</v>
       </c>
       <c r="O32">
-        <v>-0.05423808400000007</v>
+        <v>-0.06472268680000007</v>
       </c>
       <c r="P32">
-        <v>-0.2312255160000003</v>
+        <v>-0.2759230332000003</v>
       </c>
       <c r="Q32">
-        <v>3.708774484</v>
+        <v>3.6640769668</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1489908694668956</v>
+        <v>0.1504863893142419</v>
       </c>
       <c r="T32">
-        <v>1.739946305444776</v>
+        <v>1.765162918567164</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.1572369214279311</v>
+        <v>0.1521647626721914</v>
       </c>
       <c r="W32">
-        <v>0.1237176199343797</v>
+        <v>0.1244622128397223</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.827562744357532</v>
+        <v>0.800867171958902</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1424188946071408</v>
+        <v>0.161670573796466</v>
       </c>
       <c r="C33">
-        <v>21.3120057737781</v>
+        <v>17.67117875012321</v>
       </c>
       <c r="D33">
-        <v>30.1549057737781</v>
+        <v>26.88997875012321</v>
       </c>
       <c r="E33">
-        <v>9.8629</v>
+        <v>10.2388</v>
       </c>
       <c r="F33">
-        <v>11.6529</v>
+        <v>12.0288</v>
       </c>
       <c r="G33">
         <v>2.81</v>
@@ -3987,45 +3987,45 @@
         <v>1.37</v>
       </c>
       <c r="M33">
-        <v>1.71064572</v>
+        <v>2.41538304</v>
       </c>
       <c r="N33">
-        <v>-0.3406457200000004</v>
+        <v>-1.04538304</v>
       </c>
       <c r="O33">
-        <v>-0.06472268680000007</v>
+        <v>-0.1986227776</v>
       </c>
       <c r="P33">
-        <v>-0.2759230332000003</v>
+        <v>-0.8467602623999999</v>
       </c>
       <c r="Q33">
-        <v>3.6640769668</v>
+        <v>3.0932397376</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1504863893142419</v>
+        <v>0.1534401291414001</v>
       </c>
       <c r="T33">
-        <v>1.765162918567164</v>
+        <v>1.814967215459515</v>
       </c>
       <c r="U33">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.1521647626721914</v>
+        <v>0.1077675862127441</v>
       </c>
       <c r="W33">
-        <v>0.1244622128397223</v>
+        <v>0.179160268688481</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y33">
-        <v>0.800867171958902</v>
+        <v>0.5671978221723375</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.161670573796466</v>
+        <v>0.163220573796466</v>
       </c>
       <c r="C34">
-        <v>17.67117875012321</v>
+        <v>17.06289829165287</v>
       </c>
       <c r="D34">
-        <v>26.88997875012321</v>
+        <v>26.65759829165287</v>
       </c>
       <c r="E34">
-        <v>10.2388</v>
+        <v>10.6147</v>
       </c>
       <c r="F34">
-        <v>12.0288</v>
+        <v>12.4047</v>
       </c>
       <c r="G34">
         <v>2.81</v>
@@ -4069,37 +4069,37 @@
         <v>1.37</v>
       </c>
       <c r="M34">
-        <v>2.41538304</v>
+        <v>2.49086376</v>
       </c>
       <c r="N34">
-        <v>-1.04538304</v>
+        <v>-1.12086376</v>
       </c>
       <c r="O34">
-        <v>-0.1986227776</v>
+        <v>-0.2129641144</v>
       </c>
       <c r="P34">
-        <v>-0.8467602623999999</v>
+        <v>-0.9078996456000001</v>
       </c>
       <c r="Q34">
-        <v>3.0932397376</v>
+        <v>3.0321003544</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1534401291414001</v>
+        <v>0.1550466982330628</v>
       </c>
       <c r="T34">
-        <v>1.814967215459515</v>
+        <v>1.842056278376821</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.1077675862127441</v>
+        <v>0.1045019017820549</v>
       </c>
       <c r="W34">
-        <v>0.179160268688481</v>
+        <v>0.1798160181221634</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5671978221723375</v>
+        <v>0.5500100093792363</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.163220573796466</v>
+        <v>0.164770573796466</v>
       </c>
       <c r="C35">
-        <v>17.06289829165287</v>
+        <v>16.45859983762865</v>
       </c>
       <c r="D35">
-        <v>26.65759829165287</v>
+        <v>26.42919983762865</v>
       </c>
       <c r="E35">
-        <v>10.6147</v>
+        <v>10.9906</v>
       </c>
       <c r="F35">
-        <v>12.4047</v>
+        <v>12.7806</v>
       </c>
       <c r="G35">
         <v>2.81</v>
@@ -4151,37 +4151,37 @@
         <v>1.37</v>
       </c>
       <c r="M35">
-        <v>2.49086376</v>
+        <v>2.56634448</v>
       </c>
       <c r="N35">
-        <v>-1.12086376</v>
+        <v>-1.19634448</v>
       </c>
       <c r="O35">
-        <v>-0.2129641144</v>
+        <v>-0.2273054512000001</v>
       </c>
       <c r="P35">
-        <v>-0.9078996456000001</v>
+        <v>-0.9690390288000004</v>
       </c>
       <c r="Q35">
-        <v>3.0321003544</v>
+        <v>2.970960971199999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1550466982330628</v>
+        <v>0.1567019512365941</v>
       </c>
       <c r="T35">
-        <v>1.842056278376821</v>
+        <v>1.869966221988591</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.1045019017820549</v>
+        <v>0.1014283164355239</v>
       </c>
       <c r="W35">
-        <v>0.1798160181221634</v>
+        <v>0.1804331940597468</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5500100093792363</v>
+        <v>0.533833244397494</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.164770573796466</v>
+        <v>0.166320573796466</v>
       </c>
       <c r="C36">
-        <v>16.45859983762865</v>
+        <v>15.85818190581784</v>
       </c>
       <c r="D36">
-        <v>26.42919983762865</v>
+        <v>26.20468190581784</v>
       </c>
       <c r="E36">
-        <v>10.9906</v>
+        <v>11.3665</v>
       </c>
       <c r="F36">
-        <v>12.7806</v>
+        <v>13.1565</v>
       </c>
       <c r="G36">
         <v>2.81</v>
@@ -4233,37 +4233,37 @@
         <v>1.37</v>
       </c>
       <c r="M36">
-        <v>2.56634448</v>
+        <v>2.6418252</v>
       </c>
       <c r="N36">
-        <v>-1.19634448</v>
+        <v>-1.2718252</v>
       </c>
       <c r="O36">
-        <v>-0.2273054512000001</v>
+        <v>-0.2416467880000001</v>
       </c>
       <c r="P36">
-        <v>-0.9690390288000004</v>
+        <v>-1.030178412</v>
       </c>
       <c r="Q36">
-        <v>2.970960971199999</v>
+        <v>2.909821588</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1567019512365941</v>
+        <v>0.1584081351017724</v>
       </c>
       <c r="T36">
-        <v>1.869966221988591</v>
+        <v>1.898734933096108</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1014283164355239</v>
+        <v>0.09853036453736605</v>
       </c>
       <c r="W36">
-        <v>0.1804331940597468</v>
+        <v>0.1810151028008969</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.533833244397494</v>
+        <v>0.5185808659861371</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.166320573796466</v>
+        <v>0.167870573796466</v>
       </c>
       <c r="C37">
-        <v>15.85818190581784</v>
+        <v>15.26154643333527</v>
       </c>
       <c r="D37">
-        <v>26.20468190581784</v>
+        <v>25.98394643333527</v>
       </c>
       <c r="E37">
-        <v>11.3665</v>
+        <v>11.7424</v>
       </c>
       <c r="F37">
-        <v>13.1565</v>
+        <v>13.5324</v>
       </c>
       <c r="G37">
         <v>2.81</v>
@@ -4315,37 +4315,37 @@
         <v>1.37</v>
       </c>
       <c r="M37">
-        <v>2.6418252</v>
+        <v>2.71730592</v>
       </c>
       <c r="N37">
-        <v>-1.2718252</v>
+        <v>-1.347305920000001</v>
       </c>
       <c r="O37">
-        <v>-0.2416467880000001</v>
+        <v>-0.2559881248000001</v>
       </c>
       <c r="P37">
-        <v>-1.030178412</v>
+        <v>-1.091317795200001</v>
       </c>
       <c r="Q37">
-        <v>2.909821588</v>
+        <v>2.848682204799999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1584081351017724</v>
+        <v>0.1601676372127376</v>
       </c>
       <c r="T37">
-        <v>1.898734933096108</v>
+        <v>1.928402666425734</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.09853036453736605</v>
+        <v>0.09579340996688364</v>
       </c>
       <c r="W37">
-        <v>0.1810151028008969</v>
+        <v>0.1815646832786498</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5185808659861371</v>
+        <v>0.5041758419309665</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.167870573796466</v>
+        <v>0.1827586229651552</v>
       </c>
       <c r="C38">
-        <v>15.26154643333526</v>
+        <v>12.94066649293963</v>
       </c>
       <c r="D38">
-        <v>25.98394643333526</v>
+        <v>24.03896649293963</v>
       </c>
       <c r="E38">
-        <v>11.7424</v>
+        <v>12.1183</v>
       </c>
       <c r="F38">
-        <v>13.5324</v>
+        <v>13.9083</v>
       </c>
       <c r="G38">
         <v>2.81</v>
@@ -4397,45 +4397,45 @@
         <v>1.37</v>
       </c>
       <c r="M38">
-        <v>2.717305919999999</v>
+        <v>3.27957714</v>
       </c>
       <c r="N38">
-        <v>-1.34730592</v>
+        <v>-1.90957714</v>
       </c>
       <c r="O38">
-        <v>-0.2559881247999999</v>
+        <v>-0.3628196566</v>
       </c>
       <c r="P38">
-        <v>-1.0913177952</v>
+        <v>-1.5467574834</v>
       </c>
       <c r="Q38">
-        <v>2.8486822048</v>
+        <v>2.3932425166</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1601676372127376</v>
+        <v>0.1625989475949861</v>
       </c>
       <c r="T38">
-        <v>1.928402666425734</v>
+        <v>1.969398052343477</v>
       </c>
       <c r="U38">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.09579340996688367</v>
+        <v>0.07936998853455844</v>
       </c>
       <c r="W38">
-        <v>0.1815646832786498</v>
+        <v>0.2170845567035511</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.5041758419309667</v>
+        <v>0.4177367817608338</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1827586229651552</v>
+        <v>0.1846586229651552</v>
       </c>
       <c r="C39">
-        <v>12.94066649293963</v>
+        <v>12.33730251947458</v>
       </c>
       <c r="D39">
-        <v>24.03896649293963</v>
+        <v>23.81150251947458</v>
       </c>
       <c r="E39">
-        <v>12.1183</v>
+        <v>12.4942</v>
       </c>
       <c r="F39">
-        <v>13.9083</v>
+        <v>14.2842</v>
       </c>
       <c r="G39">
         <v>2.81</v>
@@ -4479,37 +4479,37 @@
         <v>1.37</v>
       </c>
       <c r="M39">
-        <v>3.27957714</v>
+        <v>3.36821436</v>
       </c>
       <c r="N39">
-        <v>-1.90957714</v>
+        <v>-1.99821436</v>
       </c>
       <c r="O39">
-        <v>-0.3628196566</v>
+        <v>-0.3796607284</v>
       </c>
       <c r="P39">
-        <v>-1.5467574834</v>
+        <v>-1.6185536316</v>
       </c>
       <c r="Q39">
-        <v>2.3932425166</v>
+        <v>2.3214463684</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1625989475949861</v>
+        <v>0.1644828015884536</v>
       </c>
       <c r="T39">
-        <v>1.969398052343477</v>
+        <v>2.001162537058694</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.07936998853455844</v>
+        <v>0.07728130462575426</v>
       </c>
       <c r="W39">
-        <v>0.2170845567035511</v>
+        <v>0.2175770683692472</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4177367817608338</v>
+        <v>0.4067437085566015</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1846586229651552</v>
+        <v>0.1865586229651552</v>
       </c>
       <c r="C40">
-        <v>12.33730251947458</v>
+        <v>11.73820286162826</v>
       </c>
       <c r="D40">
-        <v>23.81150251947458</v>
+        <v>23.58830286162826</v>
       </c>
       <c r="E40">
-        <v>12.4942</v>
+        <v>12.8701</v>
       </c>
       <c r="F40">
-        <v>14.2842</v>
+        <v>14.6601</v>
       </c>
       <c r="G40">
         <v>2.81</v>
@@ -4561,37 +4561,37 @@
         <v>1.37</v>
       </c>
       <c r="M40">
-        <v>3.36821436</v>
+        <v>3.45685158</v>
       </c>
       <c r="N40">
-        <v>-1.99821436</v>
+        <v>-2.08685158</v>
       </c>
       <c r="O40">
-        <v>-0.3796607284</v>
+        <v>-0.3965018002</v>
       </c>
       <c r="P40">
-        <v>-1.6185536316</v>
+        <v>-1.6903497798</v>
       </c>
       <c r="Q40">
-        <v>2.3214463684</v>
+        <v>2.249650220199999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1644828015884536</v>
+        <v>0.166428421286625</v>
       </c>
       <c r="T40">
-        <v>2.001162537058694</v>
+        <v>2.033968480289165</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.07728130462575426</v>
+        <v>0.07529973271227339</v>
       </c>
       <c r="W40">
-        <v>0.2175770683692472</v>
+        <v>0.2180443230264459</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4067437085566015</v>
+        <v>0.3963143826961757</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1865586229651552</v>
+        <v>0.1884586229651552</v>
       </c>
       <c r="C41">
-        <v>11.73820286162826</v>
+        <v>11.14324871695663</v>
       </c>
       <c r="D41">
-        <v>23.58830286162826</v>
+        <v>23.36924871695663</v>
       </c>
       <c r="E41">
-        <v>12.8701</v>
+        <v>13.246</v>
       </c>
       <c r="F41">
-        <v>14.6601</v>
+        <v>15.036</v>
       </c>
       <c r="G41">
         <v>2.81</v>
@@ -4643,37 +4643,37 @@
         <v>1.37</v>
       </c>
       <c r="M41">
-        <v>3.45685158</v>
+        <v>3.5454888</v>
       </c>
       <c r="N41">
-        <v>-2.08685158</v>
+        <v>-2.175488800000001</v>
       </c>
       <c r="O41">
-        <v>-0.3965018002</v>
+        <v>-0.4133428720000001</v>
       </c>
       <c r="P41">
-        <v>-1.6903497798</v>
+        <v>-1.762145928</v>
       </c>
       <c r="Q41">
-        <v>2.249650220199999</v>
+        <v>2.177854072</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.166428421286625</v>
+        <v>0.1684388949747354</v>
       </c>
       <c r="T41">
-        <v>2.033968480289165</v>
+        <v>2.067867954960651</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.07529973271227339</v>
+        <v>0.07341723939446654</v>
       </c>
       <c r="W41">
-        <v>0.2180443230264459</v>
+        <v>0.2184882149507848</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3963143826961757</v>
+        <v>0.3864065231287713</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1884586229651552</v>
+        <v>0.1903586229651552</v>
       </c>
       <c r="C42">
-        <v>11.14324871695663</v>
+        <v>10.5523256554737</v>
       </c>
       <c r="D42">
-        <v>23.36924871695663</v>
+        <v>23.1542256554737</v>
       </c>
       <c r="E42">
-        <v>13.246</v>
+        <v>13.6219</v>
       </c>
       <c r="F42">
-        <v>15.036</v>
+        <v>15.4119</v>
       </c>
       <c r="G42">
         <v>2.81</v>
@@ -4725,37 +4725,37 @@
         <v>1.37</v>
       </c>
       <c r="M42">
-        <v>3.5454888</v>
+        <v>3.63412602</v>
       </c>
       <c r="N42">
-        <v>-2.175488800000001</v>
+        <v>-2.26412602</v>
       </c>
       <c r="O42">
-        <v>-0.4133428720000001</v>
+        <v>-0.4301839438000001</v>
       </c>
       <c r="P42">
-        <v>-1.762145928</v>
+        <v>-1.8339420762</v>
       </c>
       <c r="Q42">
-        <v>2.177854072</v>
+        <v>2.1060579238</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1684388949747354</v>
+        <v>0.1705175203132902</v>
       </c>
       <c r="T42">
-        <v>2.067867954960651</v>
+        <v>2.102916564366763</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.07341723939446654</v>
+        <v>0.07162657501899176</v>
       </c>
       <c r="W42">
-        <v>0.2184882149507848</v>
+        <v>0.2189104536105217</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3864065231287713</v>
+        <v>0.3769819737841671</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1903586229651552</v>
+        <v>0.1922586229651552</v>
       </c>
       <c r="C43">
-        <v>10.5523256554737</v>
+        <v>9.965323420328236</v>
       </c>
       <c r="D43">
-        <v>23.1542256554737</v>
+        <v>22.94312342032824</v>
       </c>
       <c r="E43">
-        <v>13.6219</v>
+        <v>13.9978</v>
       </c>
       <c r="F43">
-        <v>15.4119</v>
+        <v>15.7878</v>
       </c>
       <c r="G43">
         <v>2.81</v>
@@ -4807,37 +4807,37 @@
         <v>1.37</v>
       </c>
       <c r="M43">
-        <v>3.63412602</v>
+        <v>3.72276324</v>
       </c>
       <c r="N43">
-        <v>-2.26412602</v>
+        <v>-2.352763240000001</v>
       </c>
       <c r="O43">
-        <v>-0.4301839438000001</v>
+        <v>-0.4470250156000001</v>
       </c>
       <c r="P43">
-        <v>-1.8339420762</v>
+        <v>-1.905738224400001</v>
       </c>
       <c r="Q43">
-        <v>2.1060579238</v>
+        <v>2.034261775599999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1705175203132902</v>
+        <v>0.1726678223876573</v>
       </c>
       <c r="T43">
-        <v>2.102916564366763</v>
+        <v>2.139173746511018</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.07162657501899176</v>
+        <v>0.06992118037568242</v>
       </c>
       <c r="W43">
-        <v>0.2189104536105217</v>
+        <v>0.2193125856674141</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3769819737841671</v>
+        <v>0.3680062125035917</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1922586229651552</v>
+        <v>0.1941586229651552</v>
       </c>
       <c r="C44">
-        <v>9.965323420328239</v>
+        <v>9.382135739285513</v>
       </c>
       <c r="D44">
-        <v>22.94312342032824</v>
+        <v>22.73583573928551</v>
       </c>
       <c r="E44">
-        <v>13.9978</v>
+        <v>14.3737</v>
       </c>
       <c r="F44">
-        <v>15.7878</v>
+        <v>16.1637</v>
       </c>
       <c r="G44">
         <v>2.81</v>
@@ -4889,37 +4889,37 @@
         <v>1.37</v>
       </c>
       <c r="M44">
-        <v>3.722763239999999</v>
+        <v>3.81140046</v>
       </c>
       <c r="N44">
-        <v>-2.35276324</v>
+        <v>-2.44140046</v>
       </c>
       <c r="O44">
-        <v>-0.4470250156</v>
+        <v>-0.4638660874</v>
       </c>
       <c r="P44">
-        <v>-1.9057382244</v>
+        <v>-1.9775343726</v>
       </c>
       <c r="Q44">
-        <v>2.0342617756</v>
+        <v>1.9624656274</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1726678223876573</v>
+        <v>0.1748935736576162</v>
       </c>
       <c r="T44">
-        <v>2.139173746511018</v>
+        <v>2.176703110484895</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06992118037568244</v>
+        <v>0.06829510641345726</v>
       </c>
       <c r="W44">
-        <v>0.2193125856674141</v>
+        <v>0.2196960139077068</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3680062125035918</v>
+        <v>0.3594479284918803</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1941586229651552</v>
+        <v>0.1960586229651552</v>
       </c>
       <c r="C45">
-        <v>9.382135739285513</v>
+        <v>8.80266014633694</v>
       </c>
       <c r="D45">
-        <v>22.73583573928551</v>
+        <v>22.53226014633694</v>
       </c>
       <c r="E45">
-        <v>14.3737</v>
+        <v>14.7496</v>
       </c>
       <c r="F45">
-        <v>16.1637</v>
+        <v>16.5396</v>
       </c>
       <c r="G45">
         <v>2.81</v>
@@ -4971,37 +4971,37 @@
         <v>1.37</v>
       </c>
       <c r="M45">
-        <v>3.81140046</v>
+        <v>3.90003768</v>
       </c>
       <c r="N45">
-        <v>-2.44140046</v>
+        <v>-2.53003768</v>
       </c>
       <c r="O45">
-        <v>-0.4638660874</v>
+        <v>-0.4807071592000001</v>
       </c>
       <c r="P45">
-        <v>-1.9775343726</v>
+        <v>-2.0493305208</v>
       </c>
       <c r="Q45">
-        <v>1.9624656274</v>
+        <v>1.8906694792</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1748935736576162</v>
+        <v>0.1771988160443594</v>
       </c>
       <c r="T45">
-        <v>2.176703110484895</v>
+        <v>2.215572808886411</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06829510641345726</v>
+        <v>0.06674294490406049</v>
       </c>
       <c r="W45">
-        <v>0.2196960139077068</v>
+        <v>0.2200620135916225</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3594479284918803</v>
+        <v>0.3512786573897921</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1960586229651552</v>
+        <v>0.1979586229651552</v>
       </c>
       <c r="C46">
-        <v>8.80266014633694</v>
+        <v>8.226797812808513</v>
       </c>
       <c r="D46">
-        <v>22.53226014633694</v>
+        <v>22.33229781280851</v>
       </c>
       <c r="E46">
-        <v>14.7496</v>
+        <v>15.1255</v>
       </c>
       <c r="F46">
-        <v>16.5396</v>
+        <v>16.9155</v>
       </c>
       <c r="G46">
         <v>2.81</v>
@@ -5053,37 +5053,37 @@
         <v>1.37</v>
       </c>
       <c r="M46">
-        <v>3.90003768</v>
+        <v>3.988674899999999</v>
       </c>
       <c r="N46">
-        <v>-2.53003768</v>
+        <v>-2.6186749</v>
       </c>
       <c r="O46">
-        <v>-0.4807071592000001</v>
+        <v>-0.497548231</v>
       </c>
       <c r="P46">
-        <v>-2.0493305208</v>
+        <v>-2.121126669</v>
       </c>
       <c r="Q46">
-        <v>1.8906694792</v>
+        <v>1.818873331</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1771988160443594</v>
+        <v>0.1795878854269841</v>
       </c>
       <c r="T46">
-        <v>2.215572808886411</v>
+        <v>2.255855950866164</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.06674294490406049</v>
+        <v>0.06525976835063695</v>
       </c>
       <c r="W46">
-        <v>0.2200620135916225</v>
+        <v>0.2204117466229198</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3512786573897921</v>
+        <v>0.3434724650033524</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1979586229651552</v>
+        <v>0.1998586229651552</v>
       </c>
       <c r="C47">
-        <v>8.226797812808513</v>
+        <v>7.654453387383036</v>
       </c>
       <c r="D47">
-        <v>22.33229781280851</v>
+        <v>22.13585338738304</v>
       </c>
       <c r="E47">
-        <v>15.1255</v>
+        <v>15.5014</v>
       </c>
       <c r="F47">
-        <v>16.9155</v>
+        <v>17.2914</v>
       </c>
       <c r="G47">
         <v>2.81</v>
@@ -5135,37 +5135,37 @@
         <v>1.37</v>
       </c>
       <c r="M47">
-        <v>3.988674899999999</v>
+        <v>4.07731212</v>
       </c>
       <c r="N47">
-        <v>-2.6186749</v>
+        <v>-2.707312120000001</v>
       </c>
       <c r="O47">
-        <v>-0.497548231</v>
+        <v>-0.5143893028000001</v>
       </c>
       <c r="P47">
-        <v>-2.121126669</v>
+        <v>-2.1929228172</v>
       </c>
       <c r="Q47">
-        <v>1.818873331</v>
+        <v>1.7470771828</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1795878854269841</v>
+        <v>0.1820654388608171</v>
       </c>
       <c r="T47">
-        <v>2.255855950866164</v>
+        <v>2.29763106106739</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.06525976835063695</v>
+        <v>0.06384107773431873</v>
       </c>
       <c r="W47">
-        <v>0.2204117466229198</v>
+        <v>0.2207462738702477</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3434724650033524</v>
+        <v>0.3360056722858881</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1998586229651552</v>
+        <v>0.2017586229651552</v>
       </c>
       <c r="C48">
-        <v>7.654453387383036</v>
+        <v>7.085534844492212</v>
       </c>
       <c r="D48">
-        <v>22.13585338738304</v>
+        <v>21.94283484449221</v>
       </c>
       <c r="E48">
-        <v>15.5014</v>
+        <v>15.8773</v>
       </c>
       <c r="F48">
-        <v>17.2914</v>
+        <v>17.6673</v>
       </c>
       <c r="G48">
         <v>2.81</v>
@@ -5217,37 +5217,37 @@
         <v>1.37</v>
       </c>
       <c r="M48">
-        <v>4.07731212</v>
+        <v>4.16594934</v>
       </c>
       <c r="N48">
-        <v>-2.707312120000001</v>
+        <v>-2.79594934</v>
       </c>
       <c r="O48">
-        <v>-0.5143893028000001</v>
+        <v>-0.5312303746000001</v>
       </c>
       <c r="P48">
-        <v>-2.1929228172</v>
+        <v>-2.2647189654</v>
       </c>
       <c r="Q48">
-        <v>1.7470771828</v>
+        <v>1.6752810346</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1820654388608171</v>
+        <v>0.1846364848770589</v>
       </c>
       <c r="T48">
-        <v>2.29763106106739</v>
+        <v>2.340982590521491</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.06384107773431873</v>
+        <v>0.06248275693146089</v>
       </c>
       <c r="W48">
-        <v>0.2207462738702477</v>
+        <v>0.2210665659155615</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3360056722858881</v>
+        <v>0.3288566154287416</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2017586229651552</v>
+        <v>0.2036586229651552</v>
       </c>
       <c r="C49">
-        <v>7.085534844492212</v>
+        <v>6.519953340571927</v>
       </c>
       <c r="D49">
-        <v>21.94283484449221</v>
+        <v>21.75315334057193</v>
       </c>
       <c r="E49">
-        <v>15.8773</v>
+        <v>16.2532</v>
       </c>
       <c r="F49">
-        <v>17.6673</v>
+        <v>18.0432</v>
       </c>
       <c r="G49">
         <v>2.81</v>
@@ -5299,37 +5299,37 @@
         <v>1.37</v>
       </c>
       <c r="M49">
-        <v>4.16594934</v>
+        <v>4.25458656</v>
       </c>
       <c r="N49">
-        <v>-2.79594934</v>
+        <v>-2.88458656</v>
       </c>
       <c r="O49">
-        <v>-0.5312303746000001</v>
+        <v>-0.5480714464000001</v>
       </c>
       <c r="P49">
-        <v>-2.2647189654</v>
+        <v>-2.3365151136</v>
       </c>
       <c r="Q49">
-        <v>1.6752810346</v>
+        <v>1.6034848864</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1846364848770589</v>
+        <v>0.1873064172785409</v>
       </c>
       <c r="T49">
-        <v>2.340982590521491</v>
+        <v>2.386001486493059</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.06248275693146089</v>
+        <v>0.06118103282872213</v>
       </c>
       <c r="W49">
-        <v>0.2210665659155615</v>
+        <v>0.2213735124589873</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3288566154287416</v>
+        <v>0.3220054359406428</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2036586229651552</v>
+        <v>0.2055586229651551</v>
       </c>
       <c r="C50">
-        <v>6.519953340571927</v>
+        <v>5.957623077709197</v>
       </c>
       <c r="D50">
-        <v>21.75315334057193</v>
+        <v>21.5667230777092</v>
       </c>
       <c r="E50">
-        <v>16.2532</v>
+        <v>16.6291</v>
       </c>
       <c r="F50">
-        <v>18.0432</v>
+        <v>18.4191</v>
       </c>
       <c r="G50">
         <v>2.81</v>
@@ -5381,37 +5381,37 @@
         <v>1.37</v>
       </c>
       <c r="M50">
-        <v>4.25458656</v>
+        <v>4.34322378</v>
       </c>
       <c r="N50">
-        <v>-2.88458656</v>
+        <v>-2.97322378</v>
       </c>
       <c r="O50">
-        <v>-0.5480714464000001</v>
+        <v>-0.5649125182</v>
       </c>
       <c r="P50">
-        <v>-2.3365151136</v>
+        <v>-2.4083112618</v>
       </c>
       <c r="Q50">
-        <v>1.6034848864</v>
+        <v>1.5316887382</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1873064172785409</v>
+        <v>0.1900810529114534</v>
       </c>
       <c r="T50">
-        <v>2.386001486493059</v>
+        <v>2.432785829365471</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.06118103282872213</v>
+        <v>0.05993244032201352</v>
       </c>
       <c r="W50">
-        <v>0.2213735124589873</v>
+        <v>0.2216679305720692</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3220054359406428</v>
+        <v>0.3154338964316501</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2055586229651551</v>
+        <v>0.2074586229651552</v>
       </c>
       <c r="C51">
-        <v>5.957623077709197</v>
+        <v>5.398461174240996</v>
       </c>
       <c r="D51">
-        <v>21.5667230777092</v>
+        <v>21.383461174241</v>
       </c>
       <c r="E51">
-        <v>16.6291</v>
+        <v>17.005</v>
       </c>
       <c r="F51">
-        <v>18.4191</v>
+        <v>18.795</v>
       </c>
       <c r="G51">
         <v>2.81</v>
@@ -5463,37 +5463,37 @@
         <v>1.37</v>
       </c>
       <c r="M51">
-        <v>4.34322378</v>
+        <v>4.431861</v>
       </c>
       <c r="N51">
-        <v>-2.97322378</v>
+        <v>-3.061861</v>
       </c>
       <c r="O51">
-        <v>-0.5649125182</v>
+        <v>-0.58175359</v>
       </c>
       <c r="P51">
-        <v>-2.4083112618</v>
+        <v>-2.48010741</v>
       </c>
       <c r="Q51">
-        <v>1.5316887382</v>
+        <v>1.45989259</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1900810529114534</v>
+        <v>0.1929666739696825</v>
       </c>
       <c r="T51">
-        <v>2.432785829365471</v>
+        <v>2.481441545952781</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05993244032201352</v>
+        <v>0.05873379151557325</v>
       </c>
       <c r="W51">
-        <v>0.2216679305720692</v>
+        <v>0.2219505719606278</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3154338964316501</v>
+        <v>0.3091252185030171</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2074586229651552</v>
+        <v>0.2093586229651552</v>
       </c>
       <c r="C52">
-        <v>5.398461174240996</v>
+        <v>4.842387541894986</v>
       </c>
       <c r="D52">
-        <v>21.383461174241</v>
+        <v>21.20328754189499</v>
       </c>
       <c r="E52">
-        <v>17.005</v>
+        <v>17.3809</v>
       </c>
       <c r="F52">
-        <v>18.795</v>
+        <v>19.1709</v>
       </c>
       <c r="G52">
         <v>2.81</v>
@@ -5545,37 +5545,37 @@
         <v>1.37</v>
       </c>
       <c r="M52">
-        <v>4.431861</v>
+        <v>4.52049822</v>
       </c>
       <c r="N52">
-        <v>-3.061861</v>
+        <v>-3.150498220000001</v>
       </c>
       <c r="O52">
-        <v>-0.58175359</v>
+        <v>-0.5985946618000001</v>
       </c>
       <c r="P52">
-        <v>-2.48010741</v>
+        <v>-2.551903558200001</v>
       </c>
       <c r="Q52">
-        <v>1.45989259</v>
+        <v>1.388096441799999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1929666739696825</v>
+        <v>0.1959700754792679</v>
       </c>
       <c r="T52">
-        <v>2.481441545952781</v>
+        <v>2.532083210155899</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05873379151557325</v>
+        <v>0.05758214854467964</v>
       </c>
       <c r="W52">
-        <v>0.2219505719606278</v>
+        <v>0.2222221293731645</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3091252185030171</v>
+        <v>0.3030639397088403</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2093586229651552</v>
+        <v>0.2112586229651552</v>
       </c>
       <c r="C53">
-        <v>4.842387541894986</v>
+        <v>4.289324769089497</v>
       </c>
       <c r="D53">
-        <v>21.20328754189499</v>
+        <v>21.0261247690895</v>
       </c>
       <c r="E53">
-        <v>17.3809</v>
+        <v>17.7568</v>
       </c>
       <c r="F53">
-        <v>19.1709</v>
+        <v>19.5468</v>
       </c>
       <c r="G53">
         <v>2.81</v>
@@ -5627,37 +5627,37 @@
         <v>1.37</v>
       </c>
       <c r="M53">
-        <v>4.52049822</v>
+        <v>4.609135439999999</v>
       </c>
       <c r="N53">
-        <v>-3.150498220000001</v>
+        <v>-3.23913544</v>
       </c>
       <c r="O53">
-        <v>-0.5985946618000001</v>
+        <v>-0.6154357335999999</v>
       </c>
       <c r="P53">
-        <v>-2.551903558200001</v>
+        <v>-2.6236997064</v>
       </c>
       <c r="Q53">
-        <v>1.388096441799999</v>
+        <v>1.3163002936</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1959700754792679</v>
+        <v>0.1990986187184193</v>
       </c>
       <c r="T53">
-        <v>2.532083210155899</v>
+        <v>2.584834943700814</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05758214854467964</v>
+        <v>0.05647479953420505</v>
       </c>
       <c r="W53">
-        <v>0.2222221293731645</v>
+        <v>0.2224832422698345</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3030639397088403</v>
+        <v>0.2972357870221318</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2112586229651552</v>
+        <v>0.2131586229651551</v>
       </c>
       <c r="C54">
-        <v>4.289324769089497</v>
+        <v>3.739198010035459</v>
       </c>
       <c r="D54">
-        <v>21.0261247690895</v>
+        <v>20.85189801003546</v>
       </c>
       <c r="E54">
-        <v>17.7568</v>
+        <v>18.1327</v>
       </c>
       <c r="F54">
-        <v>19.5468</v>
+        <v>19.9227</v>
       </c>
       <c r="G54">
         <v>2.81</v>
@@ -5709,37 +5709,37 @@
         <v>1.37</v>
       </c>
       <c r="M54">
-        <v>4.609135439999999</v>
+        <v>4.69777266</v>
       </c>
       <c r="N54">
-        <v>-3.23913544</v>
+        <v>-3.32777266</v>
       </c>
       <c r="O54">
-        <v>-0.6154357335999999</v>
+        <v>-0.6322768054000001</v>
       </c>
       <c r="P54">
-        <v>-2.6236997064</v>
+        <v>-2.6954958546</v>
       </c>
       <c r="Q54">
-        <v>1.3163002936</v>
+        <v>1.2445041454</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1990986187184193</v>
+        <v>0.202360291457109</v>
       </c>
       <c r="T54">
-        <v>2.584834943700814</v>
+        <v>2.639831431864661</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05647479953420505</v>
+        <v>0.05540923727884268</v>
       </c>
       <c r="W54">
-        <v>0.2224832422698345</v>
+        <v>0.2227345018496489</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2972357870221318</v>
+        <v>0.2916275646254878</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2131586229651551</v>
+        <v>0.2150586229651552</v>
       </c>
       <c r="C55">
-        <v>3.739198010035459</v>
+        <v>3.19193487930665</v>
       </c>
       <c r="D55">
-        <v>20.85189801003546</v>
+        <v>20.68053487930665</v>
       </c>
       <c r="E55">
-        <v>18.1327</v>
+        <v>18.5086</v>
       </c>
       <c r="F55">
-        <v>19.9227</v>
+        <v>20.2986</v>
       </c>
       <c r="G55">
         <v>2.81</v>
@@ -5791,37 +5791,37 @@
         <v>1.37</v>
       </c>
       <c r="M55">
-        <v>4.69777266</v>
+        <v>4.78640988</v>
       </c>
       <c r="N55">
-        <v>-3.32777266</v>
+        <v>-3.41640988</v>
       </c>
       <c r="O55">
-        <v>-0.6322768054000001</v>
+        <v>-0.6491178772</v>
       </c>
       <c r="P55">
-        <v>-2.6954958546</v>
+        <v>-2.7672920028</v>
       </c>
       <c r="Q55">
-        <v>1.2445041454</v>
+        <v>1.1727079972</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.202360291457109</v>
+        <v>0.2057637760540027</v>
       </c>
       <c r="T55">
-        <v>2.639831431864661</v>
+        <v>2.697219071687805</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05540923727884268</v>
+        <v>0.05438314029219745</v>
       </c>
       <c r="W55">
-        <v>0.2227345018496489</v>
+        <v>0.2229764555190998</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2916275646254878</v>
+        <v>0.2862270541694603</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2150586229651552</v>
+        <v>0.2169586229651552</v>
       </c>
       <c r="C56">
-        <v>3.19193487930665</v>
+        <v>2.647465351566137</v>
       </c>
       <c r="D56">
-        <v>20.68053487930665</v>
+        <v>20.51196535156614</v>
       </c>
       <c r="E56">
-        <v>18.5086</v>
+        <v>18.8845</v>
       </c>
       <c r="F56">
-        <v>20.2986</v>
+        <v>20.6745</v>
       </c>
       <c r="G56">
         <v>2.81</v>
@@ -5873,37 +5873,37 @@
         <v>1.37</v>
       </c>
       <c r="M56">
-        <v>4.78640988</v>
+        <v>4.8750471</v>
       </c>
       <c r="N56">
-        <v>-3.41640988</v>
+        <v>-3.5050471</v>
       </c>
       <c r="O56">
-        <v>-0.6491178772</v>
+        <v>-0.6659589490000001</v>
       </c>
       <c r="P56">
-        <v>-2.7672920028</v>
+        <v>-2.839088151</v>
       </c>
       <c r="Q56">
-        <v>1.1727079972</v>
+        <v>1.100911849</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2057637760540027</v>
+        <v>0.2093185266329806</v>
       </c>
       <c r="T56">
-        <v>2.697219071687805</v>
+        <v>2.757157273280868</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05438314029219745</v>
+        <v>0.05339435592324841</v>
       </c>
       <c r="W56">
-        <v>0.2229764555190998</v>
+        <v>0.223209610873298</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2862270541694603</v>
+        <v>0.2810229259118338</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2169586229651552</v>
+        <v>0.2188586229651552</v>
       </c>
       <c r="C57">
-        <v>2.647465351566137</v>
+        <v>2.105721666157059</v>
       </c>
       <c r="D57">
-        <v>20.51196535156614</v>
+        <v>20.34612166615706</v>
       </c>
       <c r="E57">
-        <v>18.8845</v>
+        <v>19.2604</v>
       </c>
       <c r="F57">
-        <v>20.6745</v>
+        <v>21.0504</v>
       </c>
       <c r="G57">
         <v>2.81</v>
@@ -5955,37 +5955,37 @@
         <v>1.37</v>
       </c>
       <c r="M57">
-        <v>4.8750471</v>
+        <v>4.96368432</v>
       </c>
       <c r="N57">
-        <v>-3.5050471</v>
+        <v>-3.593684320000001</v>
       </c>
       <c r="O57">
-        <v>-0.6659589490000001</v>
+        <v>-0.6828000208000001</v>
       </c>
       <c r="P57">
-        <v>-2.839088151</v>
+        <v>-2.910884299200001</v>
       </c>
       <c r="Q57">
-        <v>1.100911849</v>
+        <v>1.029115700799999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2093185266329806</v>
+        <v>0.2130348567837301</v>
       </c>
       <c r="T57">
-        <v>2.757157273280868</v>
+        <v>2.819819938582705</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05339435592324841</v>
+        <v>0.05244088528176181</v>
       </c>
       <c r="W57">
-        <v>0.223209610873298</v>
+        <v>0.2234344392505606</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2810229259118338</v>
+        <v>0.2760046593776938</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2188586229651552</v>
+        <v>0.2207586229651552</v>
       </c>
       <c r="C58">
-        <v>2.105721666157059</v>
+        <v>1.566638236284806</v>
       </c>
       <c r="D58">
-        <v>20.34612166615706</v>
+        <v>20.18293823628481</v>
       </c>
       <c r="E58">
-        <v>19.2604</v>
+        <v>19.6363</v>
       </c>
       <c r="F58">
-        <v>21.0504</v>
+        <v>21.4263</v>
       </c>
       <c r="G58">
         <v>2.81</v>
@@ -6037,37 +6037,37 @@
         <v>1.37</v>
       </c>
       <c r="M58">
-        <v>4.96368432</v>
+        <v>5.05232154</v>
       </c>
       <c r="N58">
-        <v>-3.593684320000001</v>
+        <v>-3.682321540000001</v>
       </c>
       <c r="O58">
-        <v>-0.6828000208000001</v>
+        <v>-0.6996410926000002</v>
       </c>
       <c r="P58">
-        <v>-2.910884299200001</v>
+        <v>-2.9826804474</v>
       </c>
       <c r="Q58">
-        <v>1.029115700799999</v>
+        <v>0.9573195525999996</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2130348567837301</v>
+        <v>0.2169240394996308</v>
       </c>
       <c r="T58">
-        <v>2.819819938582705</v>
+        <v>2.885397146456722</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05244088528176181</v>
+        <v>0.05152086975050284</v>
       </c>
       <c r="W58">
-        <v>0.2234344392505606</v>
+        <v>0.2236513789128314</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2760046593776938</v>
+        <v>0.2711624723710676</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2207586229651552</v>
+        <v>0.2226586229651552</v>
       </c>
       <c r="C59">
-        <v>1.566638236284806</v>
+        <v>1.030151562534741</v>
       </c>
       <c r="D59">
-        <v>20.18293823628481</v>
+        <v>20.02235156253474</v>
       </c>
       <c r="E59">
-        <v>19.6363</v>
+        <v>20.0122</v>
       </c>
       <c r="F59">
-        <v>21.4263</v>
+        <v>21.8022</v>
       </c>
       <c r="G59">
         <v>2.81</v>
@@ -6119,37 +6119,37 @@
         <v>1.37</v>
       </c>
       <c r="M59">
-        <v>5.05232154</v>
+        <v>5.14095876</v>
       </c>
       <c r="N59">
-        <v>-3.682321540000001</v>
+        <v>-3.770958760000001</v>
       </c>
       <c r="O59">
-        <v>-0.6996410926000002</v>
+        <v>-0.7164821644000001</v>
       </c>
       <c r="P59">
-        <v>-2.9826804474</v>
+        <v>-3.054476595600001</v>
       </c>
       <c r="Q59">
-        <v>0.9573195525999996</v>
+        <v>0.8855234043999993</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2169240394996308</v>
+        <v>0.2209984213924792</v>
       </c>
       <c r="T59">
-        <v>2.885397146456722</v>
+        <v>2.954097078515216</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05152086975050284</v>
+        <v>0.05063257889273556</v>
       </c>
       <c r="W59">
-        <v>0.2236513789128314</v>
+        <v>0.223860837897093</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2711624723710676</v>
+        <v>0.2664872573301871</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2226586229651552</v>
+        <v>0.2245586229651552</v>
       </c>
       <c r="C60">
-        <v>1.030151562534748</v>
+        <v>0.4962001504858939</v>
       </c>
       <c r="D60">
-        <v>20.02235156253474</v>
+        <v>19.86430015048589</v>
       </c>
       <c r="E60">
-        <v>20.0122</v>
+        <v>20.3881</v>
       </c>
       <c r="F60">
-        <v>21.8022</v>
+        <v>22.1781</v>
       </c>
       <c r="G60">
         <v>2.81</v>
@@ -6201,37 +6201,37 @@
         <v>1.37</v>
       </c>
       <c r="M60">
-        <v>5.140958759999999</v>
+        <v>5.229595979999999</v>
       </c>
       <c r="N60">
-        <v>-3.77095876</v>
+        <v>-3.859595979999999</v>
       </c>
       <c r="O60">
-        <v>-0.7164821643999999</v>
+        <v>-0.7333232362</v>
       </c>
       <c r="P60">
-        <v>-3.0544765956</v>
+        <v>-3.1262727438</v>
       </c>
       <c r="Q60">
-        <v>0.8855234044000002</v>
+        <v>0.8137272562000004</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2209984213924791</v>
+        <v>0.225271553621564</v>
       </c>
       <c r="T60">
-        <v>2.954097078515215</v>
+        <v>3.026148226771683</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05063257889273556</v>
+        <v>0.04977439958946886</v>
       </c>
       <c r="W60">
-        <v>0.223860837897093</v>
+        <v>0.2240631965768033</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2664872573301872</v>
+        <v>0.2619705241550992</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2245586229651552</v>
+        <v>0.2264586229651551</v>
       </c>
       <c r="C61">
-        <v>0.4962001504858939</v>
+        <v>-0.03527556780380792</v>
       </c>
       <c r="D61">
-        <v>19.86430015048589</v>
+        <v>19.70872443219619</v>
       </c>
       <c r="E61">
-        <v>20.3881</v>
+        <v>20.764</v>
       </c>
       <c r="F61">
-        <v>22.1781</v>
+        <v>22.554</v>
       </c>
       <c r="G61">
         <v>2.81</v>
@@ -6283,37 +6283,37 @@
         <v>1.37</v>
       </c>
       <c r="M61">
-        <v>5.229595979999999</v>
+        <v>5.3182332</v>
       </c>
       <c r="N61">
-        <v>-3.859595979999999</v>
+        <v>-3.9482332</v>
       </c>
       <c r="O61">
-        <v>-0.7333232362</v>
+        <v>-0.750164308</v>
       </c>
       <c r="P61">
-        <v>-3.1262727438</v>
+        <v>-3.198068892</v>
       </c>
       <c r="Q61">
-        <v>0.8137272562000004</v>
+        <v>0.7419311079999997</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.225271553621564</v>
+        <v>0.2297583424621031</v>
       </c>
       <c r="T61">
-        <v>3.026148226771683</v>
+        <v>3.101801932440975</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04977439958946886</v>
+        <v>0.0489448262629777</v>
       </c>
       <c r="W61">
-        <v>0.2240631965768033</v>
+        <v>0.2242588099671899</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2619705241550992</v>
+        <v>0.2576043487525143</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2264586229651551</v>
+        <v>0.2283586229651552</v>
       </c>
       <c r="C62">
-        <v>-0.03527556780380792</v>
+        <v>-0.5643333086514843</v>
       </c>
       <c r="D62">
-        <v>19.70872443219619</v>
+        <v>19.55556669134851</v>
       </c>
       <c r="E62">
-        <v>20.764</v>
+        <v>21.1399</v>
       </c>
       <c r="F62">
-        <v>22.554</v>
+        <v>22.9299</v>
       </c>
       <c r="G62">
         <v>2.81</v>
@@ -6365,37 +6365,37 @@
         <v>1.37</v>
       </c>
       <c r="M62">
-        <v>5.3182332</v>
+        <v>5.40687042</v>
       </c>
       <c r="N62">
-        <v>-3.9482332</v>
+        <v>-4.03687042</v>
       </c>
       <c r="O62">
-        <v>-0.750164308</v>
+        <v>-0.7670053797999999</v>
       </c>
       <c r="P62">
-        <v>-3.198068892</v>
+        <v>-3.2698650402</v>
       </c>
       <c r="Q62">
-        <v>0.7419311079999997</v>
+        <v>0.6701349598000004</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2297583424621031</v>
+        <v>0.2344752230380545</v>
       </c>
       <c r="T62">
-        <v>3.101801932440975</v>
+        <v>3.181335315324078</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0489448262629777</v>
+        <v>0.04814245206194528</v>
       </c>
       <c r="W62">
-        <v>0.2242588099671899</v>
+        <v>0.2244480098037933</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2576043487525143</v>
+        <v>0.2533813266418173</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2283586229651552</v>
+        <v>0.2302586229651552</v>
       </c>
       <c r="C63">
-        <v>-0.5643333086514843</v>
+        <v>-1.09102900814003</v>
       </c>
       <c r="D63">
-        <v>19.55556669134851</v>
+        <v>19.40477099185997</v>
       </c>
       <c r="E63">
-        <v>21.1399</v>
+        <v>21.5158</v>
       </c>
       <c r="F63">
-        <v>22.9299</v>
+        <v>23.3058</v>
       </c>
       <c r="G63">
         <v>2.81</v>
@@ -6447,37 +6447,37 @@
         <v>1.37</v>
       </c>
       <c r="M63">
-        <v>5.40687042</v>
+        <v>5.49550764</v>
       </c>
       <c r="N63">
-        <v>-4.03687042</v>
+        <v>-4.12550764</v>
       </c>
       <c r="O63">
-        <v>-0.7670053797999999</v>
+        <v>-0.7838464516000001</v>
       </c>
       <c r="P63">
-        <v>-3.2698650402</v>
+        <v>-3.3416611884</v>
       </c>
       <c r="Q63">
-        <v>0.6701349598000004</v>
+        <v>0.5983388115999997</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2344752230380545</v>
+        <v>0.2394403604864243</v>
       </c>
       <c r="T63">
-        <v>3.181335315324078</v>
+        <v>3.265054665727343</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04814245206194528</v>
+        <v>0.04736596089965584</v>
       </c>
       <c r="W63">
-        <v>0.2244480098037933</v>
+        <v>0.2246311064198612</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2533813266418173</v>
+        <v>0.2492945310508201</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2302586229651552</v>
+        <v>0.2321586229651552</v>
       </c>
       <c r="C64">
-        <v>-1.09102900814003</v>
+        <v>-1.615416890230993</v>
       </c>
       <c r="D64">
-        <v>19.40477099185997</v>
+        <v>19.25628310976901</v>
       </c>
       <c r="E64">
-        <v>21.5158</v>
+        <v>21.8917</v>
       </c>
       <c r="F64">
-        <v>23.3058</v>
+        <v>23.6817</v>
       </c>
       <c r="G64">
         <v>2.81</v>
@@ -6529,37 +6529,37 @@
         <v>1.37</v>
       </c>
       <c r="M64">
-        <v>5.49550764</v>
+        <v>5.58414486</v>
       </c>
       <c r="N64">
-        <v>-4.12550764</v>
+        <v>-4.214144860000001</v>
       </c>
       <c r="O64">
-        <v>-0.7838464516000001</v>
+        <v>-0.8006875234000003</v>
       </c>
       <c r="P64">
-        <v>-3.3416611884</v>
+        <v>-3.413457336600001</v>
       </c>
       <c r="Q64">
-        <v>0.5983388115999997</v>
+        <v>0.526542663399999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2394403604864243</v>
+        <v>0.2446738837428142</v>
       </c>
       <c r="T64">
-        <v>3.265054665727343</v>
+        <v>3.353299386422676</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04736596089965584</v>
+        <v>0.04661412025045495</v>
       </c>
       <c r="W64">
-        <v>0.2246311064198612</v>
+        <v>0.2248083904449427</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2492945310508201</v>
+        <v>0.2453374750023944</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2321586229651552</v>
+        <v>0.2340586229651552</v>
       </c>
       <c r="C65">
-        <v>-1.615416890230993</v>
+        <v>-2.137549531774077</v>
       </c>
       <c r="D65">
-        <v>19.25628310976901</v>
+        <v>19.11005046822592</v>
       </c>
       <c r="E65">
-        <v>21.8917</v>
+        <v>22.2676</v>
       </c>
       <c r="F65">
-        <v>23.6817</v>
+        <v>24.0576</v>
       </c>
       <c r="G65">
         <v>2.81</v>
@@ -6611,37 +6611,37 @@
         <v>1.37</v>
       </c>
       <c r="M65">
-        <v>5.58414486</v>
+        <v>5.672782079999999</v>
       </c>
       <c r="N65">
-        <v>-4.214144860000001</v>
+        <v>-4.30278208</v>
       </c>
       <c r="O65">
-        <v>-0.8006875234000003</v>
+        <v>-0.8175285952</v>
       </c>
       <c r="P65">
-        <v>-3.413457336600001</v>
+        <v>-3.4852534848</v>
       </c>
       <c r="Q65">
-        <v>0.526542663399999</v>
+        <v>0.4547465151999996</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2446738837428142</v>
+        <v>0.2501981582912257</v>
       </c>
       <c r="T65">
-        <v>3.353299386422676</v>
+        <v>3.446446591601084</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04661412025045495</v>
+        <v>0.0458857746215416</v>
       </c>
       <c r="W65">
-        <v>0.2248083904449427</v>
+        <v>0.2249801343442405</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2453374750023944</v>
+        <v>0.241504076955482</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2340586229651552</v>
+        <v>0.2359586229651552</v>
       </c>
       <c r="C66">
-        <v>-2.137549531774077</v>
+        <v>-2.657477924576774</v>
       </c>
       <c r="D66">
-        <v>19.11005046822592</v>
+        <v>18.96602207542323</v>
       </c>
       <c r="E66">
-        <v>22.2676</v>
+        <v>22.6435</v>
       </c>
       <c r="F66">
-        <v>24.0576</v>
+        <v>24.4335</v>
       </c>
       <c r="G66">
         <v>2.81</v>
@@ -6693,37 +6693,37 @@
         <v>1.37</v>
       </c>
       <c r="M66">
-        <v>5.672782079999999</v>
+        <v>5.7614193</v>
       </c>
       <c r="N66">
-        <v>-4.30278208</v>
+        <v>-4.391419300000001</v>
       </c>
       <c r="O66">
-        <v>-0.8175285952</v>
+        <v>-0.8343696670000001</v>
       </c>
       <c r="P66">
-        <v>-3.4852534848</v>
+        <v>-3.557049633000001</v>
       </c>
       <c r="Q66">
-        <v>0.4547465151999996</v>
+        <v>0.3829503669999994</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2501981582912257</v>
+        <v>0.256038105670975</v>
       </c>
       <c r="T66">
-        <v>3.446446591601084</v>
+        <v>3.544916494218258</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0458857746215416</v>
+        <v>0.04517983962736403</v>
       </c>
       <c r="W66">
-        <v>0.2249801343442405</v>
+        <v>0.2251465938158676</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.241504076955482</v>
+        <v>0.2377886296177053</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2359586229651552</v>
+        <v>0.2378586229651552</v>
       </c>
       <c r="C67">
-        <v>-2.657477924576774</v>
+        <v>-3.175251534688169</v>
       </c>
       <c r="D67">
-        <v>18.96602207542323</v>
+        <v>18.82414846531183</v>
       </c>
       <c r="E67">
-        <v>22.6435</v>
+        <v>23.0194</v>
       </c>
       <c r="F67">
-        <v>24.4335</v>
+        <v>24.8094</v>
       </c>
       <c r="G67">
         <v>2.81</v>
@@ -6775,37 +6775,37 @@
         <v>1.37</v>
       </c>
       <c r="M67">
-        <v>5.7614193</v>
+        <v>5.85005652</v>
       </c>
       <c r="N67">
-        <v>-4.391419300000001</v>
+        <v>-4.48005652</v>
       </c>
       <c r="O67">
-        <v>-0.8343696670000001</v>
+        <v>-0.8512107388</v>
       </c>
       <c r="P67">
-        <v>-3.557049633000001</v>
+        <v>-3.6288457812</v>
       </c>
       <c r="Q67">
-        <v>0.3829503669999994</v>
+        <v>0.3111542188</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.256038105670975</v>
+        <v>0.2622215793671802</v>
       </c>
       <c r="T67">
-        <v>3.544916494218258</v>
+        <v>3.649178744048207</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04517983962736403</v>
+        <v>0.044495296602707</v>
       </c>
       <c r="W67">
-        <v>0.2251465938158676</v>
+        <v>0.2253080090610817</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2377886296177053</v>
+        <v>0.2341857715931949</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2378586229651552</v>
+        <v>0.2397586229651552</v>
       </c>
       <c r="C68">
-        <v>-3.175251534688169</v>
+        <v>-3.690918359041742</v>
       </c>
       <c r="D68">
-        <v>18.82414846531183</v>
+        <v>18.68438164095826</v>
       </c>
       <c r="E68">
-        <v>23.0194</v>
+        <v>23.3953</v>
       </c>
       <c r="F68">
-        <v>24.8094</v>
+        <v>25.1853</v>
       </c>
       <c r="G68">
         <v>2.81</v>
@@ -6857,37 +6857,37 @@
         <v>1.37</v>
       </c>
       <c r="M68">
-        <v>5.85005652</v>
+        <v>5.93869374</v>
       </c>
       <c r="N68">
-        <v>-4.48005652</v>
+        <v>-4.568693740000001</v>
       </c>
       <c r="O68">
-        <v>-0.8512107388</v>
+        <v>-0.8680518106000001</v>
       </c>
       <c r="P68">
-        <v>-3.6288457812</v>
+        <v>-3.700641929400001</v>
       </c>
       <c r="Q68">
-        <v>0.3111542188</v>
+        <v>0.2393580705999994</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2622215793671802</v>
+        <v>0.2687798090449735</v>
       </c>
       <c r="T68">
-        <v>3.649178744048207</v>
+        <v>3.759759918110274</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.044495296602707</v>
+        <v>0.04383118769818899</v>
       </c>
       <c r="W68">
-        <v>0.2253080090610817</v>
+        <v>0.2254646059407671</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2341857715931949</v>
+        <v>0.2306904615694156</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2397586229651552</v>
+        <v>0.2416586229651552</v>
       </c>
       <c r="C69">
-        <v>-3.690918359041742</v>
+        <v>-4.204524979593362</v>
       </c>
       <c r="D69">
-        <v>18.68438164095826</v>
+        <v>18.54667502040664</v>
       </c>
       <c r="E69">
-        <v>23.3953</v>
+        <v>23.7712</v>
       </c>
       <c r="F69">
-        <v>25.1853</v>
+        <v>25.5612</v>
       </c>
       <c r="G69">
         <v>2.81</v>
@@ -6939,37 +6939,37 @@
         <v>1.37</v>
       </c>
       <c r="M69">
-        <v>5.93869374</v>
+        <v>6.02733096</v>
       </c>
       <c r="N69">
-        <v>-4.568693740000001</v>
+        <v>-4.657330960000001</v>
       </c>
       <c r="O69">
-        <v>-0.8680518106000001</v>
+        <v>-0.8848928824000002</v>
       </c>
       <c r="P69">
-        <v>-3.700641929400001</v>
+        <v>-3.772438077600001</v>
       </c>
       <c r="Q69">
-        <v>0.2393580705999994</v>
+        <v>0.1675619223999987</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2687798090449735</v>
+        <v>0.2757479280776289</v>
       </c>
       <c r="T69">
-        <v>3.759759918110274</v>
+        <v>3.87725241555122</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04383118769818899</v>
+        <v>0.04318661140850973</v>
       </c>
       <c r="W69">
-        <v>0.2254646059407671</v>
+        <v>0.2256165970298734</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2306904615694156</v>
+        <v>0.2272979547816301</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2416586229651552</v>
+        <v>0.2435586229651552</v>
       </c>
       <c r="C70">
-        <v>-4.204524979593362</v>
+        <v>-4.716116615082729</v>
       </c>
       <c r="D70">
-        <v>18.54667502040664</v>
+        <v>18.41098338491727</v>
       </c>
       <c r="E70">
-        <v>23.7712</v>
+        <v>24.1471</v>
       </c>
       <c r="F70">
-        <v>25.5612</v>
+        <v>25.9371</v>
       </c>
       <c r="G70">
         <v>2.81</v>
@@ -7021,37 +7021,37 @@
         <v>1.37</v>
       </c>
       <c r="M70">
-        <v>6.02733096</v>
+        <v>6.11596818</v>
       </c>
       <c r="N70">
-        <v>-4.657330960000001</v>
+        <v>-4.74596818</v>
       </c>
       <c r="O70">
-        <v>-0.8848928824000002</v>
+        <v>-0.9017339542</v>
       </c>
       <c r="P70">
-        <v>-3.772438077600001</v>
+        <v>-3.8442342258</v>
       </c>
       <c r="Q70">
-        <v>0.1675619223999987</v>
+        <v>0.09576577419999976</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2757479280776289</v>
+        <v>0.2831656031769073</v>
       </c>
       <c r="T70">
-        <v>3.87725241555122</v>
+        <v>4.002325074117389</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04318661140850973</v>
+        <v>0.04256071848954582</v>
       </c>
       <c r="W70">
-        <v>0.2256165970298734</v>
+        <v>0.2257641825801651</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2272979547816301</v>
+        <v>0.2240037815239254</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2435586229651552</v>
+        <v>0.2454586229651552</v>
       </c>
       <c r="C71">
-        <v>-4.716116615082729</v>
+        <v>-5.225737170539141</v>
       </c>
       <c r="D71">
-        <v>18.41098338491727</v>
+        <v>18.27726282946086</v>
       </c>
       <c r="E71">
-        <v>24.1471</v>
+        <v>24.523</v>
       </c>
       <c r="F71">
-        <v>25.9371</v>
+        <v>26.313</v>
       </c>
       <c r="G71">
         <v>2.81</v>
@@ -7103,37 +7103,37 @@
         <v>1.37</v>
       </c>
       <c r="M71">
-        <v>6.11596818</v>
+        <v>6.2046054</v>
       </c>
       <c r="N71">
-        <v>-4.74596818</v>
+        <v>-4.834605400000001</v>
       </c>
       <c r="O71">
-        <v>-0.9017339542</v>
+        <v>-0.9185750260000002</v>
       </c>
       <c r="P71">
-        <v>-3.8442342258</v>
+        <v>-3.916030374000001</v>
       </c>
       <c r="Q71">
-        <v>0.09576577419999976</v>
+        <v>0.02396962599999908</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2831656031769073</v>
+        <v>0.2910777899494709</v>
       </c>
       <c r="T71">
-        <v>4.002325074117389</v>
+        <v>4.135735909921302</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04256071848954582</v>
+        <v>0.04195270822540946</v>
       </c>
       <c r="W71">
-        <v>0.2257641825801651</v>
+        <v>0.2259075514004485</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2240037815239254</v>
+        <v>0.2208037275021549</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2454586229651552</v>
+        <v>0.2473586229651552</v>
       </c>
       <c r="C72">
-        <v>-5.225737170539141</v>
+        <v>-5.733429284645503</v>
       </c>
       <c r="D72">
-        <v>18.27726282946086</v>
+        <v>18.1454707153545</v>
       </c>
       <c r="E72">
-        <v>24.523</v>
+        <v>24.8989</v>
       </c>
       <c r="F72">
-        <v>26.313</v>
+        <v>26.6889</v>
       </c>
       <c r="G72">
         <v>2.81</v>
@@ -7185,37 +7185,37 @@
         <v>1.37</v>
       </c>
       <c r="M72">
-        <v>6.2046054</v>
+        <v>6.29324262</v>
       </c>
       <c r="N72">
-        <v>-4.834605400000001</v>
+        <v>-4.92324262</v>
       </c>
       <c r="O72">
-        <v>-0.9185750260000002</v>
+        <v>-0.9354160978</v>
       </c>
       <c r="P72">
-        <v>-3.916030374000001</v>
+        <v>-3.9878265222</v>
       </c>
       <c r="Q72">
-        <v>0.02396962599999908</v>
+        <v>-0.04782652219999983</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2910777899494709</v>
+        <v>0.2995356447753147</v>
       </c>
       <c r="T72">
-        <v>4.135735909921302</v>
+        <v>4.278347493022037</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04195270822540946</v>
+        <v>0.04136182501096707</v>
       </c>
       <c r="W72">
-        <v>0.2259075514004485</v>
+        <v>0.226046881662414</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2208037275021549</v>
+        <v>0.2176938158471952</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2473586229651552</v>
+        <v>0.2492586229651552</v>
       </c>
       <c r="C73">
-        <v>-5.733429284645499</v>
+        <v>-6.239234375067714</v>
       </c>
       <c r="D73">
-        <v>18.1454707153545</v>
+        <v>18.01556562493228</v>
       </c>
       <c r="E73">
-        <v>24.8989</v>
+        <v>25.2748</v>
       </c>
       <c r="F73">
-        <v>26.6889</v>
+        <v>27.06479999999999</v>
       </c>
       <c r="G73">
         <v>2.81</v>
@@ -7267,37 +7267,37 @@
         <v>1.37</v>
       </c>
       <c r="M73">
-        <v>6.293242619999999</v>
+        <v>6.381879839999999</v>
       </c>
       <c r="N73">
-        <v>-4.92324262</v>
+        <v>-5.011879839999999</v>
       </c>
       <c r="O73">
-        <v>-0.9354160978</v>
+        <v>-0.9522571695999998</v>
       </c>
       <c r="P73">
-        <v>-3.9878265222</v>
+        <v>-4.059622670399999</v>
       </c>
       <c r="Q73">
-        <v>-0.04782652219999983</v>
+        <v>-0.1196226703999987</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2995356447753146</v>
+        <v>0.3085976320887187</v>
       </c>
       <c r="T73">
-        <v>4.278347493022036</v>
+        <v>4.431145617772822</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04136182501096707</v>
+        <v>0.04078735521914809</v>
       </c>
       <c r="W73">
-        <v>0.226046881662414</v>
+        <v>0.2261823416393249</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.217693815847195</v>
+        <v>0.2146702906270953</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2492586229651552</v>
+        <v>0.2511586229651552</v>
       </c>
       <c r="C74">
-        <v>-6.239234375067714</v>
+        <v>-6.743192681850903</v>
       </c>
       <c r="D74">
-        <v>18.01556562493228</v>
+        <v>17.88750731814909</v>
       </c>
       <c r="E74">
-        <v>25.2748</v>
+        <v>25.6507</v>
       </c>
       <c r="F74">
-        <v>27.06479999999999</v>
+        <v>27.4407</v>
       </c>
       <c r="G74">
         <v>2.81</v>
@@ -7349,37 +7349,37 @@
         <v>1.37</v>
       </c>
       <c r="M74">
-        <v>6.381879839999999</v>
+        <v>6.47051706</v>
       </c>
       <c r="N74">
-        <v>-5.011879839999999</v>
+        <v>-5.10051706</v>
       </c>
       <c r="O74">
-        <v>-0.9522571695999998</v>
+        <v>-0.9690982413999999</v>
       </c>
       <c r="P74">
-        <v>-4.059622670399999</v>
+        <v>-4.131418818599999</v>
       </c>
       <c r="Q74">
-        <v>-0.1196226703999987</v>
+        <v>-0.1914188185999994</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3085976320887187</v>
+        <v>0.3183308777216342</v>
       </c>
       <c r="T74">
-        <v>4.431145617772822</v>
+        <v>4.595262122134779</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04078735521914809</v>
+        <v>0.0402286243257351</v>
       </c>
       <c r="W74">
-        <v>0.2261823416393249</v>
+        <v>0.2263140903839917</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2146702906270953</v>
+        <v>0.2117296017143954</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2511586229651552</v>
+        <v>0.2530586229651552</v>
       </c>
       <c r="C75">
-        <v>-6.743192681850903</v>
+        <v>-7.245343308977827</v>
       </c>
       <c r="D75">
-        <v>17.88750731814909</v>
+        <v>17.76125669102217</v>
       </c>
       <c r="E75">
-        <v>25.6507</v>
+        <v>26.0266</v>
       </c>
       <c r="F75">
-        <v>27.4407</v>
+        <v>27.8166</v>
       </c>
       <c r="G75">
         <v>2.81</v>
@@ -7431,37 +7431,37 @@
         <v>1.37</v>
       </c>
       <c r="M75">
-        <v>6.47051706</v>
+        <v>6.55915428</v>
       </c>
       <c r="N75">
-        <v>-5.10051706</v>
+        <v>-5.18915428</v>
       </c>
       <c r="O75">
-        <v>-0.9690982413999999</v>
+        <v>-0.9859393132000001</v>
       </c>
       <c r="P75">
-        <v>-4.131418818599999</v>
+        <v>-4.2032149668</v>
       </c>
       <c r="Q75">
-        <v>-0.1914188185999994</v>
+        <v>-0.2632149668000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3183308777216342</v>
+        <v>0.3288128345570817</v>
       </c>
       <c r="T75">
-        <v>4.595262122134779</v>
+        <v>4.772002972986116</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0402286243257351</v>
+        <v>0.03968499426727922</v>
       </c>
       <c r="W75">
-        <v>0.2263140903839917</v>
+        <v>0.2264422783517756</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2117296017143954</v>
+        <v>0.2088683908804169</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2530586229651552</v>
+        <v>0.2549586229651551</v>
       </c>
       <c r="C76">
-        <v>-7.245343308977827</v>
+        <v>-7.745724264179717</v>
       </c>
       <c r="D76">
-        <v>17.76125669102217</v>
+        <v>17.63677573582028</v>
       </c>
       <c r="E76">
-        <v>26.0266</v>
+        <v>26.4025</v>
       </c>
       <c r="F76">
-        <v>27.8166</v>
+        <v>28.1925</v>
       </c>
       <c r="G76">
         <v>2.81</v>
@@ -7513,37 +7513,37 @@
         <v>1.37</v>
       </c>
       <c r="M76">
-        <v>6.55915428</v>
+        <v>6.647791499999999</v>
       </c>
       <c r="N76">
-        <v>-5.18915428</v>
+        <v>-5.277791499999999</v>
       </c>
       <c r="O76">
-        <v>-0.9859393132000001</v>
+        <v>-1.002780385</v>
       </c>
       <c r="P76">
-        <v>-4.2032149668</v>
+        <v>-4.275011115</v>
       </c>
       <c r="Q76">
-        <v>-0.2632149668000001</v>
+        <v>-0.3350111149999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3288128345570817</v>
+        <v>0.3401333479393649</v>
       </c>
       <c r="T76">
-        <v>4.772002972986116</v>
+        <v>4.962883091905561</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03968499426727922</v>
+        <v>0.03915586101038216</v>
       </c>
       <c r="W76">
-        <v>0.2264422783517756</v>
+        <v>0.2265670479737519</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2088683908804169</v>
+        <v>0.2060834790020114</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2549586229651551</v>
+        <v>0.2568586229651552</v>
       </c>
       <c r="C77">
-        <v>-7.745724264179717</v>
+        <v>-8.244372497084726</v>
       </c>
       <c r="D77">
-        <v>17.63677573582028</v>
+        <v>17.51402750291527</v>
       </c>
       <c r="E77">
-        <v>26.4025</v>
+        <v>26.7784</v>
       </c>
       <c r="F77">
-        <v>28.1925</v>
+        <v>28.5684</v>
       </c>
       <c r="G77">
         <v>2.81</v>
@@ -7595,37 +7595,37 @@
         <v>1.37</v>
       </c>
       <c r="M77">
-        <v>6.647791499999999</v>
+        <v>6.736428719999999</v>
       </c>
       <c r="N77">
-        <v>-5.277791499999999</v>
+        <v>-5.36642872</v>
       </c>
       <c r="O77">
-        <v>-1.002780385</v>
+        <v>-1.0196214568</v>
       </c>
       <c r="P77">
-        <v>-4.275011115</v>
+        <v>-4.346807263200001</v>
       </c>
       <c r="Q77">
-        <v>-0.3350111149999999</v>
+        <v>-0.4068072632000006</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3401333479393649</v>
+        <v>0.3523972374368386</v>
       </c>
       <c r="T77">
-        <v>4.962883091905561</v>
+        <v>5.169669887401628</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03915586101038216</v>
+        <v>0.03864065231287713</v>
       </c>
       <c r="W77">
-        <v>0.2265670479737519</v>
+        <v>0.2266885341846236</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2060834790020114</v>
+        <v>0.2033718542783006</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2568586229651552</v>
+        <v>0.2587586229651552</v>
       </c>
       <c r="C78">
-        <v>-8.244372497084726</v>
+        <v>-8.74132393578423</v>
       </c>
       <c r="D78">
-        <v>17.51402750291527</v>
+        <v>17.39297606421577</v>
       </c>
       <c r="E78">
-        <v>26.7784</v>
+        <v>27.1543</v>
       </c>
       <c r="F78">
-        <v>28.5684</v>
+        <v>28.9443</v>
       </c>
       <c r="G78">
         <v>2.81</v>
@@ -7677,37 +7677,37 @@
         <v>1.37</v>
       </c>
       <c r="M78">
-        <v>6.736428719999999</v>
+        <v>6.82506594</v>
       </c>
       <c r="N78">
-        <v>-5.36642872</v>
+        <v>-5.455065940000001</v>
       </c>
       <c r="O78">
-        <v>-1.0196214568</v>
+        <v>-1.0364625286</v>
       </c>
       <c r="P78">
-        <v>-4.346807263200001</v>
+        <v>-4.4186034114</v>
       </c>
       <c r="Q78">
-        <v>-0.4068072632000006</v>
+        <v>-0.4786034114000004</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3523972374368386</v>
+        <v>0.3657275521080054</v>
       </c>
       <c r="T78">
-        <v>5.169669887401628</v>
+        <v>5.39443814337561</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03864065231287713</v>
+        <v>0.03813882565946315</v>
       </c>
       <c r="W78">
-        <v>0.2266885341846236</v>
+        <v>0.2268068649094986</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2033718542783006</v>
+        <v>0.2007306613655955</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2587586229651552</v>
+        <v>0.2606586229651552</v>
       </c>
       <c r="C79">
-        <v>-8.74132393578423</v>
+        <v>-9.236613521893258</v>
       </c>
       <c r="D79">
-        <v>17.39297606421577</v>
+        <v>17.27358647810674</v>
       </c>
       <c r="E79">
-        <v>27.1543</v>
+        <v>27.5302</v>
       </c>
       <c r="F79">
-        <v>28.9443</v>
+        <v>29.3202</v>
       </c>
       <c r="G79">
         <v>2.81</v>
@@ -7759,37 +7759,37 @@
         <v>1.37</v>
       </c>
       <c r="M79">
-        <v>6.82506594</v>
+        <v>6.91370316</v>
       </c>
       <c r="N79">
-        <v>-5.455065940000001</v>
+        <v>-5.54370316</v>
       </c>
       <c r="O79">
-        <v>-1.0364625286</v>
+        <v>-1.0533036004</v>
       </c>
       <c r="P79">
-        <v>-4.4186034114</v>
+        <v>-4.4903995596</v>
       </c>
       <c r="Q79">
-        <v>-0.4786034114000004</v>
+        <v>-0.5503995596000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3657275521080054</v>
+        <v>0.3802697135674603</v>
       </c>
       <c r="T79">
-        <v>5.39443814337561</v>
+        <v>5.639639877165411</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03813882565946315</v>
+        <v>0.03764986635613669</v>
       </c>
       <c r="W79">
-        <v>0.2268068649094986</v>
+        <v>0.226922161513223</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2007306613655955</v>
+        <v>0.198157191348088</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2606586229651552</v>
+        <v>0.2625586229651551</v>
       </c>
       <c r="C80">
-        <v>-9.236613521893258</v>
+        <v>-9.730275244176696</v>
       </c>
       <c r="D80">
-        <v>17.27358647810674</v>
+        <v>17.1558247558233</v>
       </c>
       <c r="E80">
-        <v>27.5302</v>
+        <v>27.9061</v>
       </c>
       <c r="F80">
-        <v>29.3202</v>
+        <v>29.6961</v>
       </c>
       <c r="G80">
         <v>2.81</v>
@@ -7841,37 +7841,37 @@
         <v>1.37</v>
       </c>
       <c r="M80">
-        <v>6.91370316</v>
+        <v>7.00234038</v>
       </c>
       <c r="N80">
-        <v>-5.54370316</v>
+        <v>-5.63234038</v>
       </c>
       <c r="O80">
-        <v>-1.0533036004</v>
+        <v>-1.0701446722</v>
       </c>
       <c r="P80">
-        <v>-4.4903995596</v>
+        <v>-4.562195707800001</v>
       </c>
       <c r="Q80">
-        <v>-0.5503995596000002</v>
+        <v>-0.6221957078000009</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3802697135674603</v>
+        <v>0.3961968427849584</v>
       </c>
       <c r="T80">
-        <v>5.639639877165411</v>
+        <v>5.908194157030431</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03764986635613669</v>
+        <v>0.03717328576935015</v>
       </c>
       <c r="W80">
-        <v>0.226922161513223</v>
+        <v>0.2270345392155872</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.198157191348088</v>
+        <v>0.1956488724702639</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2625586229651551</v>
+        <v>0.2644586229651552</v>
       </c>
       <c r="C81">
-        <v>-9.730275244176696</v>
+        <v>-10.22234217080941</v>
       </c>
       <c r="D81">
-        <v>17.1558247558233</v>
+        <v>17.03965782919059</v>
       </c>
       <c r="E81">
-        <v>27.9061</v>
+        <v>28.282</v>
       </c>
       <c r="F81">
-        <v>29.6961</v>
+        <v>30.072</v>
       </c>
       <c r="G81">
         <v>2.81</v>
@@ -7923,37 +7923,37 @@
         <v>1.37</v>
       </c>
       <c r="M81">
-        <v>7.00234038</v>
+        <v>7.0909776</v>
       </c>
       <c r="N81">
-        <v>-5.63234038</v>
+        <v>-5.720977600000001</v>
       </c>
       <c r="O81">
-        <v>-1.0701446722</v>
+        <v>-1.086985744</v>
       </c>
       <c r="P81">
-        <v>-4.562195707800001</v>
+        <v>-4.633991856000002</v>
       </c>
       <c r="Q81">
-        <v>-0.6221957078000009</v>
+        <v>-0.6939918560000016</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3961968427849584</v>
+        <v>0.4137166849242063</v>
       </c>
       <c r="T81">
-        <v>5.908194157030431</v>
+        <v>6.203603864881953</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03717328576935015</v>
+        <v>0.03670861969723327</v>
       </c>
       <c r="W81">
-        <v>0.2270345392155872</v>
+        <v>0.2271441074753924</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1956488724702639</v>
+        <v>0.1932032615643856</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2644586229651552</v>
+        <v>0.2663586229651552</v>
       </c>
       <c r="C82">
-        <v>-10.22234217080941</v>
+        <v>-10.71284648033445</v>
       </c>
       <c r="D82">
-        <v>17.03965782919059</v>
+        <v>16.92505351966555</v>
       </c>
       <c r="E82">
-        <v>28.282</v>
+        <v>28.6579</v>
       </c>
       <c r="F82">
-        <v>30.072</v>
+        <v>30.4479</v>
       </c>
       <c r="G82">
         <v>2.81</v>
@@ -8005,37 +8005,37 @@
         <v>1.37</v>
       </c>
       <c r="M82">
-        <v>7.0909776</v>
+        <v>7.17961482</v>
       </c>
       <c r="N82">
-        <v>-5.720977600000001</v>
+        <v>-5.80961482</v>
       </c>
       <c r="O82">
-        <v>-1.086985744</v>
+        <v>-1.1038268158</v>
       </c>
       <c r="P82">
-        <v>-4.633991856000002</v>
+        <v>-4.7057880042</v>
       </c>
       <c r="Q82">
-        <v>-0.6939918560000016</v>
+        <v>-0.7657880042000005</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4137166849242063</v>
+        <v>0.4330807209728487</v>
       </c>
       <c r="T82">
-        <v>6.203603864881953</v>
+        <v>6.530109331454687</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03670861969723327</v>
+        <v>0.03625542686146496</v>
       </c>
       <c r="W82">
-        <v>0.2271441074753924</v>
+        <v>0.2272509703460666</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1932032615643856</v>
+        <v>0.1908180361129735</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2663586229651552</v>
+        <v>0.2682586229651552</v>
       </c>
       <c r="C83">
-        <v>-10.71284648033445</v>
+        <v>-11.20181949138037</v>
       </c>
       <c r="D83">
-        <v>16.92505351966555</v>
+        <v>16.81198050861963</v>
       </c>
       <c r="E83">
-        <v>28.6579</v>
+        <v>29.0338</v>
       </c>
       <c r="F83">
-        <v>30.4479</v>
+        <v>30.8238</v>
       </c>
       <c r="G83">
         <v>2.81</v>
@@ -8087,37 +8087,37 @@
         <v>1.37</v>
       </c>
       <c r="M83">
-        <v>7.17961482</v>
+        <v>7.26825204</v>
       </c>
       <c r="N83">
-        <v>-5.80961482</v>
+        <v>-5.898252040000001</v>
       </c>
       <c r="O83">
-        <v>-1.1038268158</v>
+        <v>-1.1206678876</v>
       </c>
       <c r="P83">
-        <v>-4.7057880042</v>
+        <v>-4.777584152400001</v>
       </c>
       <c r="Q83">
-        <v>-0.7657880042000005</v>
+        <v>-0.8375841524000012</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4330807209728487</v>
+        <v>0.4545963165824515</v>
       </c>
       <c r="T83">
-        <v>6.530109331454687</v>
+        <v>6.892893183202171</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03625542686146496</v>
+        <v>0.03581328750949588</v>
       </c>
       <c r="W83">
-        <v>0.2272509703460666</v>
+        <v>0.2273552268052609</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1908180361129735</v>
+        <v>0.1884909868920835</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2682586229651552</v>
+        <v>0.2701586229651552</v>
       </c>
       <c r="C84">
-        <v>-11.20181949138037</v>
+        <v>-11.6892916911952</v>
       </c>
       <c r="D84">
-        <v>16.81198050861963</v>
+        <v>16.7004083088048</v>
       </c>
       <c r="E84">
-        <v>29.0338</v>
+        <v>29.4097</v>
       </c>
       <c r="F84">
-        <v>30.8238</v>
+        <v>31.1997</v>
       </c>
       <c r="G84">
         <v>2.81</v>
@@ -8169,37 +8169,37 @@
         <v>1.37</v>
       </c>
       <c r="M84">
-        <v>7.26825204</v>
+        <v>7.35688926</v>
       </c>
       <c r="N84">
-        <v>-5.898252040000001</v>
+        <v>-5.98688926</v>
       </c>
       <c r="O84">
-        <v>-1.1206678876</v>
+        <v>-1.1375089594</v>
       </c>
       <c r="P84">
-        <v>-4.777584152400001</v>
+        <v>-4.8493803006</v>
       </c>
       <c r="Q84">
-        <v>-0.8375841524000012</v>
+        <v>-0.9093803006000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4545963165824515</v>
+        <v>0.4786431587343604</v>
       </c>
       <c r="T84">
-        <v>6.892893183202171</v>
+        <v>7.298357488096416</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03581328750949588</v>
+        <v>0.03538180211781521</v>
       </c>
       <c r="W84">
-        <v>0.2273552268052609</v>
+        <v>0.2274569710606192</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1884909868920835</v>
+        <v>0.1862200111463959</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2701586229651552</v>
+        <v>0.2720586229651552</v>
       </c>
       <c r="C85">
-        <v>-11.6892916911952</v>
+        <v>-12.17529276305174</v>
       </c>
       <c r="D85">
-        <v>16.7004083088048</v>
+        <v>16.59030723694827</v>
       </c>
       <c r="E85">
-        <v>29.4097</v>
+        <v>29.7856</v>
       </c>
       <c r="F85">
-        <v>31.1997</v>
+        <v>31.5756</v>
       </c>
       <c r="G85">
         <v>2.81</v>
@@ -8251,37 +8251,37 @@
         <v>1.37</v>
       </c>
       <c r="M85">
-        <v>7.35688926</v>
+        <v>7.445526480000001</v>
       </c>
       <c r="N85">
-        <v>-5.98688926</v>
+        <v>-6.075526480000001</v>
       </c>
       <c r="O85">
-        <v>-1.1375089594</v>
+        <v>-1.1543500312</v>
       </c>
       <c r="P85">
-        <v>-4.8493803006</v>
+        <v>-4.921176448800001</v>
       </c>
       <c r="Q85">
-        <v>-0.9093803006000001</v>
+        <v>-0.9811764488000008</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4786431587343604</v>
+        <v>0.505695856155258</v>
       </c>
       <c r="T85">
-        <v>7.298357488096416</v>
+        <v>7.754504831102444</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03538180211781521</v>
+        <v>0.03496059018784121</v>
       </c>
       <c r="W85">
-        <v>0.2274569710606192</v>
+        <v>0.227556292833707</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1862200111463959</v>
+        <v>0.1840031062517959</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2720586229651552</v>
+        <v>0.2739586229651552</v>
       </c>
       <c r="C86">
-        <v>-12.17529276305173</v>
+        <v>-12.65985161257586</v>
       </c>
       <c r="D86">
-        <v>16.59030723694827</v>
+        <v>16.48164838742414</v>
       </c>
       <c r="E86">
-        <v>29.7856</v>
+        <v>30.1615</v>
       </c>
       <c r="F86">
-        <v>31.57559999999999</v>
+        <v>31.9515</v>
       </c>
       <c r="G86">
         <v>2.81</v>
@@ -8333,37 +8333,37 @@
         <v>1.37</v>
       </c>
       <c r="M86">
-        <v>7.445526479999999</v>
+        <v>7.5341637</v>
       </c>
       <c r="N86">
-        <v>-6.075526479999999</v>
+        <v>-6.1641637</v>
       </c>
       <c r="O86">
-        <v>-1.1543500312</v>
+        <v>-1.171191103</v>
       </c>
       <c r="P86">
-        <v>-4.921176448799999</v>
+        <v>-4.992972597</v>
       </c>
       <c r="Q86">
-        <v>-0.981176448799999</v>
+        <v>-1.052972597</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5056958561552577</v>
+        <v>0.5363555798989416</v>
       </c>
       <c r="T86">
-        <v>7.754504831102439</v>
+        <v>8.271471819842601</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03496059018784122</v>
+        <v>0.03454928912680779</v>
       </c>
       <c r="W86">
-        <v>0.227556292833707</v>
+        <v>0.2276532776238987</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1840031062517959</v>
+        <v>0.1818383638253042</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2739586229651552</v>
+        <v>0.2758586229651552</v>
       </c>
       <c r="C87">
-        <v>-12.65985161257586</v>
+        <v>-13.142996393047</v>
       </c>
       <c r="D87">
-        <v>16.48164838742414</v>
+        <v>16.374403606953</v>
       </c>
       <c r="E87">
-        <v>30.1615</v>
+        <v>30.5374</v>
       </c>
       <c r="F87">
-        <v>31.9515</v>
+        <v>32.3274</v>
       </c>
       <c r="G87">
         <v>2.81</v>
@@ -8415,37 +8415,37 @@
         <v>1.37</v>
       </c>
       <c r="M87">
-        <v>7.5341637</v>
+        <v>7.62280092</v>
       </c>
       <c r="N87">
-        <v>-6.1641637</v>
+        <v>-6.25280092</v>
       </c>
       <c r="O87">
-        <v>-1.171191103</v>
+        <v>-1.1880321748</v>
       </c>
       <c r="P87">
-        <v>-4.992972597</v>
+        <v>-5.0647687452</v>
       </c>
       <c r="Q87">
-        <v>-1.052972597</v>
+        <v>-1.1247687452</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5363555798989416</v>
+        <v>0.5713952641774374</v>
       </c>
       <c r="T87">
-        <v>8.271471819842601</v>
+        <v>8.862291235545644</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03454928912680779</v>
+        <v>0.03414755320672863</v>
       </c>
       <c r="W87">
-        <v>0.2276532776238987</v>
+        <v>0.2277480069538534</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1818383638253042</v>
+        <v>0.1797239642459401</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2758586229651552</v>
+        <v>0.2777586229651552</v>
       </c>
       <c r="C88">
-        <v>-13.142996393047</v>
+        <v>-13.62475452971715</v>
       </c>
       <c r="D88">
-        <v>16.374403606953</v>
+        <v>16.26854547028285</v>
       </c>
       <c r="E88">
-        <v>30.5374</v>
+        <v>30.9133</v>
       </c>
       <c r="F88">
-        <v>32.3274</v>
+        <v>32.7033</v>
       </c>
       <c r="G88">
         <v>2.81</v>
@@ -8497,37 +8497,37 @@
         <v>1.37</v>
       </c>
       <c r="M88">
-        <v>7.62280092</v>
+        <v>7.71143814</v>
       </c>
       <c r="N88">
-        <v>-6.25280092</v>
+        <v>-6.341438140000001</v>
       </c>
       <c r="O88">
-        <v>-1.1880321748</v>
+        <v>-1.2048732466</v>
       </c>
       <c r="P88">
-        <v>-5.0647687452</v>
+        <v>-5.136564893400001</v>
       </c>
       <c r="Q88">
-        <v>-1.1247687452</v>
+        <v>-1.196564893400001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5713952641774374</v>
+        <v>0.6118256691141634</v>
       </c>
       <c r="T88">
-        <v>8.862291235545644</v>
+        <v>9.544005945972232</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03414755320672863</v>
+        <v>0.03375505259515703</v>
       </c>
       <c r="W88">
-        <v>0.2277480069538534</v>
+        <v>0.227840558598062</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1797239642459401</v>
+        <v>0.177658171553458</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2777586229651552</v>
+        <v>0.2796586229651552</v>
       </c>
       <c r="C89">
-        <v>-13.62475452971715</v>
+        <v>-14.10515274319268</v>
       </c>
       <c r="D89">
-        <v>16.26854547028285</v>
+        <v>16.16404725680732</v>
       </c>
       <c r="E89">
-        <v>30.9133</v>
+        <v>31.2892</v>
       </c>
       <c r="F89">
-        <v>32.7033</v>
+        <v>33.0792</v>
       </c>
       <c r="G89">
         <v>2.81</v>
@@ -8579,37 +8579,37 @@
         <v>1.37</v>
       </c>
       <c r="M89">
-        <v>7.71143814</v>
+        <v>7.80007536</v>
       </c>
       <c r="N89">
-        <v>-6.341438140000001</v>
+        <v>-6.43007536</v>
       </c>
       <c r="O89">
-        <v>-1.2048732466</v>
+        <v>-1.2217143184</v>
       </c>
       <c r="P89">
-        <v>-5.136564893400001</v>
+        <v>-5.2083610416</v>
       </c>
       <c r="Q89">
-        <v>-1.196564893400001</v>
+        <v>-1.2683610416</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6118256691141634</v>
+        <v>0.6589944748736771</v>
       </c>
       <c r="T89">
-        <v>9.544005945972232</v>
+        <v>10.33933977480326</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03375505259515703</v>
+        <v>0.03337147245203025</v>
       </c>
       <c r="W89">
-        <v>0.227840558598062</v>
+        <v>0.2279310067958113</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.177658171553458</v>
+        <v>0.1756393286948961</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2796586229651552</v>
+        <v>0.2815586229651552</v>
       </c>
       <c r="C90">
-        <v>-14.10515274319268</v>
+        <v>-14.58421707192075</v>
       </c>
       <c r="D90">
-        <v>16.16404725680732</v>
+        <v>16.06088292807924</v>
       </c>
       <c r="E90">
-        <v>31.2892</v>
+        <v>31.6651</v>
       </c>
       <c r="F90">
-        <v>33.0792</v>
+        <v>33.45509999999999</v>
       </c>
       <c r="G90">
         <v>2.81</v>
@@ -8661,37 +8661,37 @@
         <v>1.37</v>
       </c>
       <c r="M90">
-        <v>7.80007536</v>
+        <v>7.888712579999999</v>
       </c>
       <c r="N90">
-        <v>-6.43007536</v>
+        <v>-6.518712579999999</v>
       </c>
       <c r="O90">
-        <v>-1.2217143184</v>
+        <v>-1.2385553902</v>
       </c>
       <c r="P90">
-        <v>-5.2083610416</v>
+        <v>-5.280157189799999</v>
       </c>
       <c r="Q90">
-        <v>-1.2683610416</v>
+        <v>-1.340157189799999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6589944748736771</v>
+        <v>0.7147394271349203</v>
       </c>
       <c r="T90">
-        <v>10.33933977480326</v>
+        <v>11.27927975433082</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03337147245203025</v>
+        <v>0.0329965120874007</v>
       </c>
       <c r="W90">
-        <v>0.2279310067958113</v>
+        <v>0.2280194224497909</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1756393286948961</v>
+        <v>0.1736658530915827</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2815586229651552</v>
+        <v>0.2834586229651552</v>
       </c>
       <c r="C91">
-        <v>-14.58421707192075</v>
+        <v>-15.06197289382011</v>
       </c>
       <c r="D91">
-        <v>16.06088292807924</v>
+        <v>15.95902710617989</v>
       </c>
       <c r="E91">
-        <v>31.6651</v>
+        <v>32.041</v>
       </c>
       <c r="F91">
-        <v>33.45509999999999</v>
+        <v>33.831</v>
       </c>
       <c r="G91">
         <v>2.81</v>
@@ -8743,37 +8743,37 @@
         <v>1.37</v>
       </c>
       <c r="M91">
-        <v>7.888712579999999</v>
+        <v>7.977349799999999</v>
       </c>
       <c r="N91">
-        <v>-6.518712579999999</v>
+        <v>-6.6073498</v>
       </c>
       <c r="O91">
-        <v>-1.2385553902</v>
+        <v>-1.255396462</v>
       </c>
       <c r="P91">
-        <v>-5.280157189799999</v>
+        <v>-5.351953338</v>
       </c>
       <c r="Q91">
-        <v>-1.340157189799999</v>
+        <v>-1.411953338</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7147394271349203</v>
+        <v>0.7816333698484126</v>
       </c>
       <c r="T91">
-        <v>11.27927975433082</v>
+        <v>12.40720772976391</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0329965120874007</v>
+        <v>0.03262988417531847</v>
       </c>
       <c r="W91">
-        <v>0.2280194224497909</v>
+        <v>0.2281058733114599</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1736658530915827</v>
+        <v>0.1717362325016761</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2834586229651552</v>
+        <v>0.2853586229651552</v>
       </c>
       <c r="C92">
-        <v>-15.06197289382011</v>
+        <v>-15.53844494709396</v>
       </c>
       <c r="D92">
-        <v>15.95902710617989</v>
+        <v>15.85845505290604</v>
       </c>
       <c r="E92">
-        <v>32.041</v>
+        <v>32.4169</v>
       </c>
       <c r="F92">
-        <v>33.831</v>
+        <v>34.2069</v>
       </c>
       <c r="G92">
         <v>2.81</v>
@@ -8825,37 +8825,37 @@
         <v>1.37</v>
       </c>
       <c r="M92">
-        <v>7.977349799999999</v>
+        <v>8.06598702</v>
       </c>
       <c r="N92">
-        <v>-6.6073498</v>
+        <v>-6.69598702</v>
       </c>
       <c r="O92">
-        <v>-1.255396462</v>
+        <v>-1.2722375338</v>
       </c>
       <c r="P92">
-        <v>-5.351953338</v>
+        <v>-5.4237494862</v>
       </c>
       <c r="Q92">
-        <v>-1.411953338</v>
+        <v>-1.4837494862</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7816333698484126</v>
+        <v>0.8633926331649029</v>
       </c>
       <c r="T92">
-        <v>12.40720772976391</v>
+        <v>13.78578636640434</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03262988417531847</v>
+        <v>0.03227131401954574</v>
       </c>
       <c r="W92">
-        <v>0.2281058733114599</v>
+        <v>0.2281904241541911</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1717362325016761</v>
+        <v>0.1698490211555038</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2853586229651552</v>
+        <v>0.2872586229651551</v>
       </c>
       <c r="C93">
-        <v>-15.53844494709396</v>
+        <v>-16.01365735026081</v>
       </c>
       <c r="D93">
-        <v>15.85845505290604</v>
+        <v>15.75914264973919</v>
       </c>
       <c r="E93">
-        <v>32.4169</v>
+        <v>32.7928</v>
       </c>
       <c r="F93">
-        <v>34.2069</v>
+        <v>34.5828</v>
       </c>
       <c r="G93">
         <v>2.81</v>
@@ -8907,37 +8907,37 @@
         <v>1.37</v>
       </c>
       <c r="M93">
-        <v>8.06598702</v>
+        <v>8.15462424</v>
       </c>
       <c r="N93">
-        <v>-6.69598702</v>
+        <v>-6.784624240000001</v>
       </c>
       <c r="O93">
-        <v>-1.2722375338</v>
+        <v>-1.2890786056</v>
       </c>
       <c r="P93">
-        <v>-5.4237494862</v>
+        <v>-5.495545634400001</v>
       </c>
       <c r="Q93">
-        <v>-1.4837494862</v>
+        <v>-1.555545634400001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8633926331649029</v>
+        <v>0.965591712310516</v>
       </c>
       <c r="T93">
-        <v>13.78578636640434</v>
+        <v>15.50900966220489</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03227131401954574</v>
+        <v>0.03192053886715936</v>
       </c>
       <c r="W93">
-        <v>0.2281904241541911</v>
+        <v>0.2282731369351238</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1698490211555038</v>
+        <v>0.168002836142944</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2872586229651551</v>
+        <v>0.2891586229651552</v>
       </c>
       <c r="C94">
-        <v>-16.01365735026081</v>
+        <v>-16.48763362143741</v>
       </c>
       <c r="D94">
-        <v>15.75914264973919</v>
+        <v>15.66106637856259</v>
       </c>
       <c r="E94">
-        <v>32.7928</v>
+        <v>33.1687</v>
       </c>
       <c r="F94">
-        <v>34.5828</v>
+        <v>34.9587</v>
       </c>
       <c r="G94">
         <v>2.81</v>
@@ -8989,37 +8989,37 @@
         <v>1.37</v>
       </c>
       <c r="M94">
-        <v>8.15462424</v>
+        <v>8.243261460000001</v>
       </c>
       <c r="N94">
-        <v>-6.784624240000001</v>
+        <v>-6.873261460000002</v>
       </c>
       <c r="O94">
-        <v>-1.2890786056</v>
+        <v>-1.3059196774</v>
       </c>
       <c r="P94">
-        <v>-5.495545634400001</v>
+        <v>-5.567341782600002</v>
       </c>
       <c r="Q94">
-        <v>-1.555545634400001</v>
+        <v>-1.627341782600002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.965591712310516</v>
+        <v>1.096990528354876</v>
       </c>
       <c r="T94">
-        <v>15.50900966220489</v>
+        <v>17.7245824710913</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03192053886715936</v>
+        <v>0.03157730726643722</v>
       </c>
       <c r="W94">
-        <v>0.2282731369351238</v>
+        <v>0.2283540709465741</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.168002836142944</v>
+        <v>0.1661963540338801</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2891586229651552</v>
+        <v>0.2910586229651552</v>
       </c>
       <c r="C95">
-        <v>-16.48763362143741</v>
+        <v>-16.960396696906</v>
       </c>
       <c r="D95">
-        <v>15.66106637856259</v>
+        <v>15.564203303094</v>
       </c>
       <c r="E95">
-        <v>33.1687</v>
+        <v>33.5446</v>
       </c>
       <c r="F95">
-        <v>34.9587</v>
+        <v>35.3346</v>
       </c>
       <c r="G95">
         <v>2.81</v>
@@ -9071,37 +9071,37 @@
         <v>1.37</v>
       </c>
       <c r="M95">
-        <v>8.243261460000001</v>
+        <v>8.33189868</v>
       </c>
       <c r="N95">
-        <v>-6.873261460000002</v>
+        <v>-6.961898680000001</v>
       </c>
       <c r="O95">
-        <v>-1.3059196774</v>
+        <v>-1.3227607492</v>
       </c>
       <c r="P95">
-        <v>-5.567341782600002</v>
+        <v>-5.6391379308</v>
       </c>
       <c r="Q95">
-        <v>-1.627341782600002</v>
+        <v>-1.699137930800001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.096990528354876</v>
+        <v>1.272188949747355</v>
       </c>
       <c r="T95">
-        <v>17.7245824710913</v>
+        <v>20.67867954960652</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03157730726643722</v>
+        <v>0.03124137846573045</v>
       </c>
       <c r="W95">
-        <v>0.2283540709465741</v>
+        <v>0.2284332829577808</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1661963540338801</v>
+        <v>0.1644283077143707</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2910586229651552</v>
+        <v>0.2929586229651552</v>
       </c>
       <c r="C96">
-        <v>-16.960396696906</v>
+        <v>-17.43196894899686</v>
       </c>
       <c r="D96">
-        <v>15.564203303094</v>
+        <v>15.46853105100314</v>
       </c>
       <c r="E96">
-        <v>33.5446</v>
+        <v>33.9205</v>
       </c>
       <c r="F96">
-        <v>35.3346</v>
+        <v>35.7105</v>
       </c>
       <c r="G96">
         <v>2.81</v>
@@ -9153,37 +9153,37 @@
         <v>1.37</v>
       </c>
       <c r="M96">
-        <v>8.33189868</v>
+        <v>8.420535899999999</v>
       </c>
       <c r="N96">
-        <v>-6.961898680000001</v>
+        <v>-7.0505359</v>
       </c>
       <c r="O96">
-        <v>-1.3227607492</v>
+        <v>-1.339601821</v>
       </c>
       <c r="P96">
-        <v>-5.6391379308</v>
+        <v>-5.710934078999999</v>
       </c>
       <c r="Q96">
-        <v>-1.699137930800001</v>
+        <v>-1.770934078999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.272188949747355</v>
+        <v>1.517466739696827</v>
       </c>
       <c r="T96">
-        <v>20.67867954960652</v>
+        <v>24.81441545952784</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03124137846573045</v>
+        <v>0.03091252185030171</v>
       </c>
       <c r="W96">
-        <v>0.2284332829577808</v>
+        <v>0.2285108273476989</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1644283077143707</v>
+        <v>0.1626974834226406</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2929586229651552</v>
+        <v>0.2948586229651552</v>
       </c>
       <c r="C97">
-        <v>-17.43196894899686</v>
+        <v>-17.90237220331531</v>
       </c>
       <c r="D97">
-        <v>15.46853105100314</v>
+        <v>15.37402779668469</v>
       </c>
       <c r="E97">
-        <v>33.9205</v>
+        <v>34.2964</v>
       </c>
       <c r="F97">
-        <v>35.7105</v>
+        <v>36.0864</v>
       </c>
       <c r="G97">
         <v>2.81</v>
@@ -9235,37 +9235,37 @@
         <v>1.37</v>
       </c>
       <c r="M97">
-        <v>8.420535899999999</v>
+        <v>8.50917312</v>
       </c>
       <c r="N97">
-        <v>-7.0505359</v>
+        <v>-7.139173120000001</v>
       </c>
       <c r="O97">
-        <v>-1.339601821</v>
+        <v>-1.3564428928</v>
       </c>
       <c r="P97">
-        <v>-5.710934078999999</v>
+        <v>-5.7827302272</v>
       </c>
       <c r="Q97">
-        <v>-1.770934078999999</v>
+        <v>-1.8427302272</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.517466739696827</v>
+        <v>1.885383424621034</v>
       </c>
       <c r="T97">
-        <v>24.81441545952784</v>
+        <v>31.01801932440981</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03091252185030171</v>
+        <v>0.03059051641436106</v>
       </c>
       <c r="W97">
-        <v>0.2285108273476989</v>
+        <v>0.2285867562294937</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1626974834226406</v>
+        <v>0.1610027179703213</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2948586229651552</v>
+        <v>0.2967586229651551</v>
       </c>
       <c r="C98">
-        <v>-17.90237220331531</v>
+        <v>-18.37162775534104</v>
       </c>
       <c r="D98">
-        <v>15.37402779668469</v>
+        <v>15.28067224465895</v>
       </c>
       <c r="E98">
-        <v>34.2964</v>
+        <v>34.67229999999999</v>
       </c>
       <c r="F98">
-        <v>36.0864</v>
+        <v>36.46229999999999</v>
       </c>
       <c r="G98">
         <v>2.81</v>
@@ -9317,37 +9317,37 @@
         <v>1.37</v>
       </c>
       <c r="M98">
-        <v>8.50917312</v>
+        <v>8.597810339999999</v>
       </c>
       <c r="N98">
-        <v>-7.139173120000001</v>
+        <v>-7.22781034</v>
       </c>
       <c r="O98">
-        <v>-1.3564428928</v>
+        <v>-1.3732839646</v>
       </c>
       <c r="P98">
-        <v>-5.7827302272</v>
+        <v>-5.8545263754</v>
       </c>
       <c r="Q98">
-        <v>-1.8427302272</v>
+        <v>-1.9145263754</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.88538342462103</v>
+        <v>2.498577899494706</v>
       </c>
       <c r="T98">
-        <v>31.01801932440973</v>
+        <v>41.35735909921299</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03059051641436106</v>
+        <v>0.0302751502657594</v>
       </c>
       <c r="W98">
-        <v>0.2285867562294937</v>
+        <v>0.2286611195673339</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1610027179703213</v>
+        <v>0.1593428961355757</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2967586229651551</v>
+        <v>0.2986586229651552</v>
       </c>
       <c r="C99">
-        <v>-18.37162775534104</v>
+        <v>-18.83975638642645</v>
       </c>
       <c r="D99">
-        <v>15.28067224465895</v>
+        <v>15.18844361357355</v>
       </c>
       <c r="E99">
-        <v>34.67229999999999</v>
+        <v>35.04819999999999</v>
       </c>
       <c r="F99">
-        <v>36.46229999999999</v>
+        <v>36.83819999999999</v>
       </c>
       <c r="G99">
         <v>2.81</v>
@@ -9399,37 +9399,37 @@
         <v>1.37</v>
       </c>
       <c r="M99">
-        <v>8.597810339999999</v>
+        <v>8.68644756</v>
       </c>
       <c r="N99">
-        <v>-7.22781034</v>
+        <v>-7.31644756</v>
       </c>
       <c r="O99">
-        <v>-1.3732839646</v>
+        <v>-1.3901250364</v>
       </c>
       <c r="P99">
-        <v>-5.8545263754</v>
+        <v>-5.9263225236</v>
       </c>
       <c r="Q99">
-        <v>-1.9145263754</v>
+        <v>-1.9863225236</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.498577899494706</v>
+        <v>3.724966849242059</v>
       </c>
       <c r="T99">
-        <v>41.35735909921299</v>
+        <v>62.03603864881946</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0302751502657594</v>
+        <v>0.02996622016100676</v>
       </c>
       <c r="W99">
-        <v>0.2286611195673339</v>
+        <v>0.2287339652860346</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1593428961355757</v>
+        <v>0.1577169482158249</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2986586229651552</v>
+        <v>0.3005586229651552</v>
       </c>
       <c r="C100">
-        <v>-18.83975638642645</v>
+        <v>-19.30677837921884</v>
       </c>
       <c r="D100">
-        <v>15.18844361357355</v>
+        <v>15.09732162078116</v>
       </c>
       <c r="E100">
-        <v>35.04819999999999</v>
+        <v>35.4241</v>
       </c>
       <c r="F100">
-        <v>36.83819999999999</v>
+        <v>37.21409999999999</v>
       </c>
       <c r="G100">
         <v>2.81</v>
@@ -9481,37 +9481,37 @@
         <v>1.37</v>
       </c>
       <c r="M100">
-        <v>8.68644756</v>
+        <v>8.775084779999998</v>
       </c>
       <c r="N100">
-        <v>-7.31644756</v>
+        <v>-7.405084779999999</v>
       </c>
       <c r="O100">
-        <v>-1.3901250364</v>
+        <v>-1.4069661082</v>
       </c>
       <c r="P100">
-        <v>-5.9263225236</v>
+        <v>-5.998118671799999</v>
       </c>
       <c r="Q100">
-        <v>-1.9863225236</v>
+        <v>-2.0581186718</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.724966849242059</v>
+        <v>7.404133698484118</v>
       </c>
       <c r="T100">
-        <v>62.03603864881946</v>
+        <v>124.0720772976389</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02996622016100676</v>
+        <v>0.02966353106847134</v>
       </c>
       <c r="W100">
-        <v>0.2287339652860346</v>
+        <v>0.2288053393740545</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1577169482158249</v>
+        <v>0.1561238477287965</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3005586229651552</v>
-      </c>
-      <c r="C101">
-        <v>-19.30677837921884</v>
-      </c>
-      <c r="D101">
-        <v>15.09732162078116</v>
-      </c>
-      <c r="E101">
-        <v>35.4241</v>
-      </c>
-      <c r="F101">
-        <v>37.21409999999999</v>
-      </c>
-      <c r="G101">
-        <v>2.81</v>
-      </c>
-      <c r="H101">
-        <v>35.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.31</v>
-      </c>
-      <c r="K101">
-        <v>3.94</v>
-      </c>
-      <c r="L101">
-        <v>1.37</v>
-      </c>
-      <c r="M101">
-        <v>8.775084779999998</v>
-      </c>
-      <c r="N101">
-        <v>-7.405084779999999</v>
-      </c>
-      <c r="O101">
-        <v>-1.4069661082</v>
-      </c>
-      <c r="P101">
-        <v>-5.998118671799999</v>
-      </c>
-      <c r="Q101">
-        <v>-2.0581186718</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.404133698484118</v>
-      </c>
-      <c r="T101">
-        <v>124.0720772976389</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02966353106847134</v>
-      </c>
-      <c r="W101">
-        <v>0.2288053393740545</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1561238477287965</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
